--- a/research/traditional_assets/database/data/slovenia/slovenia_steel.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_steel.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.104014186154114</v>
+        <v>0.1038530092004212</v>
       </c>
       <c r="C2">
-        <v>150.698509024695</v>
+        <v>149.5302741878217</v>
       </c>
       <c r="D2">
-        <v>124.898509024695</v>
+        <v>125.2452741878217</v>
       </c>
       <c r="E2">
-        <v>-132.2</v>
+        <v>-130.685</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.515</v>
       </c>
       <c r="G2">
         <v>25.8</v>
@@ -1445,28 +1445,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.07620450000000001</v>
       </c>
       <c r="N2">
-        <v>24.80000000000001</v>
+        <v>24.72379550000001</v>
       </c>
       <c r="O2">
-        <v>4.712000000000002</v>
+        <v>4.697521145000001</v>
       </c>
       <c r="P2">
-        <v>20.08800000000001</v>
+        <v>20.02627435500001</v>
       </c>
       <c r="Q2">
-        <v>38.78800000000001</v>
+        <v>38.726274355</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.104014186154114</v>
+        <v>0.1044904840408295</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.9896058769459952</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>325.4400986818364</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1038530092004212</v>
+        <v>0.1036918322467284</v>
       </c>
       <c r="C3">
-        <v>149.5302741878217</v>
+        <v>148.3639702123659</v>
       </c>
       <c r="D3">
-        <v>125.2452741878217</v>
+        <v>125.5939702123659</v>
       </c>
       <c r="E3">
-        <v>-130.685</v>
+        <v>-129.17</v>
       </c>
       <c r="F3">
-        <v>1.515</v>
+        <v>3.03</v>
       </c>
       <c r="G3">
         <v>25.8</v>
@@ -1527,28 +1527,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M3">
-        <v>0.07620450000000001</v>
+        <v>0.152409</v>
       </c>
       <c r="N3">
-        <v>24.72379550000001</v>
+        <v>24.64759100000001</v>
       </c>
       <c r="O3">
-        <v>4.697521145000001</v>
+        <v>4.683042290000002</v>
       </c>
       <c r="P3">
-        <v>20.02627435500001</v>
+        <v>19.96454871000001</v>
       </c>
       <c r="Q3">
-        <v>38.726274355</v>
+        <v>38.66454871000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1044904840408295</v>
+        <v>0.10497650229258</v>
       </c>
       <c r="T3">
-        <v>0.9896058769459952</v>
+        <v>0.9978008428948312</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>325.4400986818364</v>
+        <v>162.7200493409182</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1036918322467284</v>
+        <v>0.1035306552930356</v>
       </c>
       <c r="C4">
-        <v>148.3639702123659</v>
+        <v>147.199613270517</v>
       </c>
       <c r="D4">
-        <v>125.5939702123659</v>
+        <v>125.944613270517</v>
       </c>
       <c r="E4">
-        <v>-129.17</v>
+        <v>-127.655</v>
       </c>
       <c r="F4">
-        <v>3.03</v>
+        <v>4.545</v>
       </c>
       <c r="G4">
         <v>25.8</v>
@@ -1609,28 +1609,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M4">
-        <v>0.152409</v>
+        <v>0.2286135</v>
       </c>
       <c r="N4">
-        <v>24.64759100000001</v>
+        <v>24.57138650000001</v>
       </c>
       <c r="O4">
-        <v>4.683042290000002</v>
+        <v>4.668563435000001</v>
       </c>
       <c r="P4">
-        <v>19.96454871000001</v>
+        <v>19.90282306500001</v>
       </c>
       <c r="Q4">
-        <v>38.66454871000001</v>
+        <v>38.60282306500001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.10497650229258</v>
+        <v>0.105472541539212</v>
       </c>
       <c r="T4">
-        <v>0.9978008428948312</v>
+        <v>1.006164777213746</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>162.7200493409182</v>
+        <v>108.4800328939455</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1035306552930356</v>
+        <v>0.1033694783393428</v>
       </c>
       <c r="C5">
-        <v>147.199613270517</v>
+        <v>146.0372197155729</v>
       </c>
       <c r="D5">
-        <v>125.944613270517</v>
+        <v>126.2972197155729</v>
       </c>
       <c r="E5">
-        <v>-127.655</v>
+        <v>-126.14</v>
       </c>
       <c r="F5">
-        <v>4.545</v>
+        <v>6.06</v>
       </c>
       <c r="G5">
         <v>25.8</v>
@@ -1691,28 +1691,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M5">
-        <v>0.2286135</v>
+        <v>0.304818</v>
       </c>
       <c r="N5">
-        <v>24.57138650000001</v>
+        <v>24.49518200000001</v>
       </c>
       <c r="O5">
-        <v>4.668563435000001</v>
+        <v>4.654084580000001</v>
       </c>
       <c r="P5">
-        <v>19.90282306500001</v>
+        <v>19.84109742</v>
       </c>
       <c r="Q5">
-        <v>38.60282306500001</v>
+        <v>38.54109742</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.105472541539212</v>
+        <v>0.1059789149368154</v>
       </c>
       <c r="T5">
-        <v>1.006164777213746</v>
+        <v>1.014702960164305</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>108.4800328939455</v>
+        <v>81.36002467045911</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1033694783393428</v>
+        <v>0.10320830138565</v>
       </c>
       <c r="C6">
-        <v>146.0372197155729</v>
+        <v>144.8768060844829</v>
       </c>
       <c r="D6">
-        <v>126.2972197155729</v>
+        <v>126.6518060844829</v>
       </c>
       <c r="E6">
-        <v>-126.14</v>
+        <v>-124.625</v>
       </c>
       <c r="F6">
-        <v>6.06</v>
+        <v>7.575</v>
       </c>
       <c r="G6">
         <v>25.8</v>
@@ -1773,28 +1773,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M6">
-        <v>0.304818</v>
+        <v>0.3810225</v>
       </c>
       <c r="N6">
-        <v>24.49518200000001</v>
+        <v>24.41897750000001</v>
       </c>
       <c r="O6">
-        <v>4.654084580000001</v>
+        <v>4.639605725000002</v>
       </c>
       <c r="P6">
-        <v>19.84109742</v>
+        <v>19.779371775</v>
       </c>
       <c r="Q6">
-        <v>38.54109742</v>
+        <v>38.479371775</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1059789149368154</v>
+        <v>0.106495948827</v>
       </c>
       <c r="T6">
-        <v>1.014702960164305</v>
+        <v>1.023420894334876</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>81.36002467045911</v>
+        <v>65.0880197363673</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.10320830138565</v>
+        <v>0.1030471244319571</v>
       </c>
       <c r="C7">
-        <v>144.8768060844829</v>
+        <v>143.7183891004325</v>
       </c>
       <c r="D7">
-        <v>126.6518060844829</v>
+        <v>127.0083891004325</v>
       </c>
       <c r="E7">
-        <v>-124.625</v>
+        <v>-123.11</v>
       </c>
       <c r="F7">
-        <v>7.575</v>
+        <v>9.09</v>
       </c>
       <c r="G7">
         <v>25.8</v>
@@ -1855,28 +1855,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M7">
-        <v>0.3810225</v>
+        <v>0.457227</v>
       </c>
       <c r="N7">
-        <v>24.41897750000001</v>
+        <v>24.34277300000001</v>
       </c>
       <c r="O7">
-        <v>4.639605725000002</v>
+        <v>4.625126870000002</v>
       </c>
       <c r="P7">
-        <v>19.779371775</v>
+        <v>19.71764613000001</v>
       </c>
       <c r="Q7">
-        <v>38.479371775</v>
+        <v>38.41764613000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.106495948827</v>
+        <v>0.1070239834382523</v>
       </c>
       <c r="T7">
-        <v>1.023420894334876</v>
+        <v>1.032324316466523</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>65.0880197363673</v>
+        <v>54.24001644697275</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1030471244319571</v>
+        <v>0.1028859474782643</v>
       </c>
       <c r="C8">
-        <v>143.7183891004325</v>
+        <v>142.5619856754729</v>
       </c>
       <c r="D8">
-        <v>127.0083891004325</v>
+        <v>127.3669856754729</v>
       </c>
       <c r="E8">
-        <v>-123.11</v>
+        <v>-121.595</v>
       </c>
       <c r="F8">
-        <v>9.09</v>
+        <v>10.605</v>
       </c>
       <c r="G8">
         <v>25.8</v>
@@ -1937,28 +1937,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M8">
-        <v>0.457227</v>
+        <v>0.5334314999999999</v>
       </c>
       <c r="N8">
-        <v>24.34277300000001</v>
+        <v>24.26656850000001</v>
       </c>
       <c r="O8">
-        <v>4.625126870000002</v>
+        <v>4.610648015000002</v>
       </c>
       <c r="P8">
-        <v>19.71764613000001</v>
+        <v>19.65592048500001</v>
       </c>
       <c r="Q8">
-        <v>38.41764613000001</v>
+        <v>38.35592048500001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1070239834382523</v>
+        <v>0.1075633736325423</v>
       </c>
       <c r="T8">
-        <v>1.032324316466523</v>
+        <v>1.041419210041862</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>54.24001644697275</v>
+        <v>46.49144266883379</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1028859474782643</v>
+        <v>0.1027247705245715</v>
       </c>
       <c r="C9">
-        <v>142.5619856754729</v>
+        <v>141.4076129131944</v>
       </c>
       <c r="D9">
-        <v>127.3669856754729</v>
+        <v>127.7276129131944</v>
       </c>
       <c r="E9">
-        <v>-121.595</v>
+        <v>-120.08</v>
       </c>
       <c r="F9">
-        <v>10.605</v>
+        <v>12.12</v>
       </c>
       <c r="G9">
         <v>25.8</v>
@@ -2019,28 +2019,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M9">
-        <v>0.5334314999999999</v>
+        <v>0.6096360000000001</v>
       </c>
       <c r="N9">
-        <v>24.26656850000001</v>
+        <v>24.19036400000001</v>
       </c>
       <c r="O9">
-        <v>4.610648015000002</v>
+        <v>4.596169160000002</v>
       </c>
       <c r="P9">
-        <v>19.65592048500001</v>
+        <v>19.59419484000001</v>
       </c>
       <c r="Q9">
-        <v>38.35592048500001</v>
+        <v>38.29419484</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1075633736325423</v>
+        <v>0.1081144897006212</v>
       </c>
       <c r="T9">
-        <v>1.041419210041862</v>
+        <v>1.050711818694924</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>46.49144266883379</v>
+        <v>40.68001233522956</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1027247705245715</v>
+        <v>0.1025635935708787</v>
       </c>
       <c r="C10">
-        <v>141.4076129131944</v>
+        <v>140.2552881114463</v>
       </c>
       <c r="D10">
-        <v>127.7276129131944</v>
+        <v>128.0902881114463</v>
       </c>
       <c r="E10">
-        <v>-120.08</v>
+        <v>-118.565</v>
       </c>
       <c r="F10">
-        <v>12.12</v>
+        <v>13.635</v>
       </c>
       <c r="G10">
         <v>25.8</v>
@@ -2101,28 +2101,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M10">
-        <v>0.6096360000000001</v>
+        <v>0.6858405</v>
       </c>
       <c r="N10">
-        <v>24.19036400000001</v>
+        <v>24.11415950000001</v>
       </c>
       <c r="O10">
-        <v>4.596169160000002</v>
+        <v>4.581690305000001</v>
       </c>
       <c r="P10">
-        <v>19.59419484000001</v>
+        <v>19.532469195</v>
       </c>
       <c r="Q10">
-        <v>38.29419484</v>
+        <v>38.23246919500001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1081144897006212</v>
+        <v>0.1086777182097568</v>
       </c>
       <c r="T10">
-        <v>1.050711818694924</v>
+        <v>1.060208660505197</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.68001233522956</v>
+        <v>36.1600109646485</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1025635935708787</v>
+        <v>0.1024024166171859</v>
       </c>
       <c r="C11">
-        <v>140.2552881114463</v>
+        <v>139.1050287651018</v>
       </c>
       <c r="D11">
-        <v>128.0902881114463</v>
+        <v>128.4550287651018</v>
       </c>
       <c r="E11">
-        <v>-118.565</v>
+        <v>-117.05</v>
       </c>
       <c r="F11">
-        <v>13.635</v>
+        <v>15.15</v>
       </c>
       <c r="G11">
         <v>25.8</v>
@@ -2183,28 +2183,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M11">
-        <v>0.6858405</v>
+        <v>0.7620449999999999</v>
       </c>
       <c r="N11">
-        <v>24.11415950000001</v>
+        <v>24.03795500000001</v>
       </c>
       <c r="O11">
-        <v>4.581690305000001</v>
+        <v>4.567211450000001</v>
       </c>
       <c r="P11">
-        <v>19.532469195</v>
+        <v>19.47074355000001</v>
       </c>
       <c r="Q11">
-        <v>38.23246919500001</v>
+        <v>38.17074355</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1086777182097568</v>
+        <v>0.1092534629079843</v>
       </c>
       <c r="T11">
-        <v>1.060208660505197</v>
+        <v>1.069916543244588</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>36.1600109646485</v>
+        <v>32.54400986818365</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1024024166171859</v>
+        <v>0.1022412396634931</v>
       </c>
       <c r="C12">
-        <v>139.1050287651018</v>
+        <v>137.9568525688723</v>
       </c>
       <c r="D12">
-        <v>128.4550287651018</v>
+        <v>128.8218525688723</v>
       </c>
       <c r="E12">
-        <v>-117.05</v>
+        <v>-115.535</v>
       </c>
       <c r="F12">
-        <v>15.15</v>
+        <v>16.665</v>
       </c>
       <c r="G12">
         <v>25.8</v>
@@ -2265,28 +2265,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M12">
-        <v>0.762045</v>
+        <v>0.8382494999999999</v>
       </c>
       <c r="N12">
-        <v>24.03795500000001</v>
+        <v>23.96175050000001</v>
       </c>
       <c r="O12">
-        <v>4.567211450000001</v>
+        <v>4.552732595000002</v>
       </c>
       <c r="P12">
-        <v>19.47074355000001</v>
+        <v>19.40901790500001</v>
       </c>
       <c r="Q12">
-        <v>38.17074355</v>
+        <v>38.109017905</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1092534629079843</v>
+        <v>0.109842145689318</v>
       </c>
       <c r="T12">
-        <v>1.069916543244588</v>
+        <v>1.079842580652279</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.54400986818365</v>
+        <v>29.5854635165306</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1022412396634931</v>
+        <v>0.1020800627098002</v>
       </c>
       <c r="C13">
-        <v>137.9568525688723</v>
+        <v>136.8107774201678</v>
       </c>
       <c r="D13">
-        <v>128.8218525688723</v>
+        <v>129.1907774201678</v>
       </c>
       <c r="E13">
-        <v>-115.535</v>
+        <v>-114.02</v>
       </c>
       <c r="F13">
-        <v>16.665</v>
+        <v>18.18</v>
       </c>
       <c r="G13">
         <v>25.8</v>
@@ -2347,28 +2347,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M13">
-        <v>0.8382494999999999</v>
+        <v>0.914454</v>
       </c>
       <c r="N13">
-        <v>23.96175050000001</v>
+        <v>23.88554600000001</v>
       </c>
       <c r="O13">
-        <v>4.552732595000002</v>
+        <v>4.538253740000002</v>
       </c>
       <c r="P13">
-        <v>19.40901790500001</v>
+        <v>19.34729226000001</v>
       </c>
       <c r="Q13">
-        <v>38.109017905</v>
+        <v>38.04729226000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.109842145689318</v>
+        <v>0.110444207624773</v>
       </c>
       <c r="T13">
-        <v>1.079842580652279</v>
+        <v>1.089994209819236</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.5854635165306</v>
+        <v>27.12000822348637</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1020800627098002</v>
+        <v>0.1019188857561074</v>
       </c>
       <c r="C14">
-        <v>136.8107774201678</v>
+        <v>135.6668214220086</v>
       </c>
       <c r="D14">
-        <v>129.1907774201678</v>
+        <v>129.5618214220086</v>
       </c>
       <c r="E14">
-        <v>-114.02</v>
+        <v>-112.505</v>
       </c>
       <c r="F14">
-        <v>18.18</v>
+        <v>19.695</v>
       </c>
       <c r="G14">
         <v>25.8</v>
@@ -2429,28 +2429,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M14">
-        <v>0.914454</v>
+        <v>0.9906585</v>
       </c>
       <c r="N14">
-        <v>23.88554600000001</v>
+        <v>23.80934150000001</v>
       </c>
       <c r="O14">
-        <v>4.538253740000002</v>
+        <v>4.523774885000002</v>
       </c>
       <c r="P14">
-        <v>19.34729226000001</v>
+        <v>19.28556661500001</v>
       </c>
       <c r="Q14">
-        <v>38.04729226000001</v>
+        <v>37.98556661500001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.110444207624773</v>
+        <v>0.1110601100644913</v>
       </c>
       <c r="T14">
-        <v>1.089994209819236</v>
+        <v>1.10037920977164</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>27.12000822348637</v>
+        <v>25.03385374475666</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1019188857561074</v>
+        <v>0.1017577088024146</v>
       </c>
       <c r="C15">
-        <v>135.6668214220086</v>
+        <v>134.5250028859857</v>
       </c>
       <c r="D15">
-        <v>129.5618214220086</v>
+        <v>129.9350028859857</v>
       </c>
       <c r="E15">
-        <v>-112.505</v>
+        <v>-110.99</v>
       </c>
       <c r="F15">
-        <v>19.695</v>
+        <v>21.21</v>
       </c>
       <c r="G15">
         <v>25.8</v>
@@ -2511,28 +2511,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M15">
-        <v>0.9906585</v>
+        <v>1.066863</v>
       </c>
       <c r="N15">
-        <v>23.80934150000001</v>
+        <v>23.73313700000001</v>
       </c>
       <c r="O15">
-        <v>4.523774885000002</v>
+        <v>4.509296030000002</v>
       </c>
       <c r="P15">
-        <v>19.28556661500001</v>
+        <v>19.22384097</v>
       </c>
       <c r="Q15">
-        <v>37.98556661500001</v>
+        <v>37.92384097</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1110601100644913</v>
+        <v>0.1116903358167612</v>
       </c>
       <c r="T15">
-        <v>1.10037920977164</v>
+        <v>1.111005721350845</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>25.03385374475666</v>
+        <v>23.24572133441689</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1017577088024146</v>
+        <v>0.1015965318487218</v>
       </c>
       <c r="C16">
-        <v>134.5250028859857</v>
+        <v>133.385340335274</v>
       </c>
       <c r="D16">
-        <v>129.9350028859857</v>
+        <v>130.3103403352739</v>
       </c>
       <c r="E16">
-        <v>-110.99</v>
+        <v>-109.475</v>
       </c>
       <c r="F16">
-        <v>21.21</v>
+        <v>22.725</v>
       </c>
       <c r="G16">
         <v>25.8</v>
@@ -2593,28 +2593,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M16">
-        <v>1.066863</v>
+        <v>1.1430675</v>
       </c>
       <c r="N16">
-        <v>23.73313700000001</v>
+        <v>23.65693250000001</v>
       </c>
       <c r="O16">
-        <v>4.509296030000002</v>
+        <v>4.494817175000001</v>
       </c>
       <c r="P16">
-        <v>19.22384097</v>
+        <v>19.16211532500001</v>
       </c>
       <c r="Q16">
-        <v>37.92384097</v>
+        <v>37.862115325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1116903358167612</v>
+        <v>0.1123353904102609</v>
       </c>
       <c r="T16">
-        <v>1.111005721350845</v>
+        <v>1.121882268496619</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>23.24572133441689</v>
+        <v>21.6960065787891</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1015965318487218</v>
+        <v>0.101435354895029</v>
       </c>
       <c r="C17">
-        <v>133.385340335274</v>
+        <v>132.2478525076964</v>
       </c>
       <c r="D17">
-        <v>130.3103403352739</v>
+        <v>130.6878525076964</v>
       </c>
       <c r="E17">
-        <v>-109.475</v>
+        <v>-107.96</v>
       </c>
       <c r="F17">
-        <v>22.725</v>
+        <v>24.24</v>
       </c>
       <c r="G17">
         <v>25.8</v>
@@ -2675,28 +2675,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M17">
-        <v>1.1430675</v>
+        <v>1.219272</v>
       </c>
       <c r="N17">
-        <v>23.65693250000001</v>
+        <v>23.58072800000001</v>
       </c>
       <c r="O17">
-        <v>4.494817175000001</v>
+        <v>4.480338320000001</v>
       </c>
       <c r="P17">
-        <v>19.16211532500001</v>
+        <v>19.10038968000001</v>
       </c>
       <c r="Q17">
-        <v>37.862115325</v>
+        <v>37.80038968000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1123353904102609</v>
+        <v>0.1129958034464631</v>
       </c>
       <c r="T17">
-        <v>1.121882268496619</v>
+        <v>1.133017781050625</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.6960065787891</v>
+        <v>20.34000616761478</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.101435354895029</v>
+        <v>0.1012741779413362</v>
       </c>
       <c r="C18">
-        <v>132.2478525076964</v>
+        <v>131.1125583588425</v>
       </c>
       <c r="D18">
-        <v>130.6878525076964</v>
+        <v>131.0675583588425</v>
       </c>
       <c r="E18">
-        <v>-107.96</v>
+        <v>-106.445</v>
       </c>
       <c r="F18">
-        <v>24.24</v>
+        <v>25.755</v>
       </c>
       <c r="G18">
         <v>25.8</v>
@@ -2757,28 +2757,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M18">
-        <v>1.219272</v>
+        <v>1.2954765</v>
       </c>
       <c r="N18">
-        <v>23.58072800000001</v>
+        <v>23.50452350000001</v>
       </c>
       <c r="O18">
-        <v>4.480338320000001</v>
+        <v>4.465859465000001</v>
       </c>
       <c r="P18">
-        <v>19.10038968000001</v>
+        <v>19.03866403500001</v>
       </c>
       <c r="Q18">
-        <v>37.80038968000001</v>
+        <v>37.73866403500001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1129958034464631</v>
+        <v>0.1136721300498026</v>
       </c>
       <c r="T18">
-        <v>1.133017781050625</v>
+        <v>1.144421619208343</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.34000616761478</v>
+        <v>19.14353521657862</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1012741779413362</v>
+        <v>0.1011130009876434</v>
       </c>
       <c r="C19">
-        <v>131.1125583588425</v>
+        <v>129.9794770652412</v>
       </c>
       <c r="D19">
-        <v>131.0675583588425</v>
+        <v>131.4494770652412</v>
       </c>
       <c r="E19">
-        <v>-106.445</v>
+        <v>-104.93</v>
       </c>
       <c r="F19">
-        <v>25.755</v>
+        <v>27.27</v>
       </c>
       <c r="G19">
         <v>25.8</v>
@@ -2839,28 +2839,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M19">
-        <v>1.2954765</v>
+        <v>1.371681</v>
       </c>
       <c r="N19">
-        <v>23.50452350000001</v>
+        <v>23.42831900000001</v>
       </c>
       <c r="O19">
-        <v>4.465859465000001</v>
+        <v>4.451380610000002</v>
       </c>
       <c r="P19">
-        <v>19.03866403500001</v>
+        <v>18.97693839000001</v>
       </c>
       <c r="Q19">
-        <v>37.73866403500001</v>
+        <v>37.67693839</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1136721300498026</v>
+        <v>0.1143649524239553</v>
       </c>
       <c r="T19">
-        <v>1.144421619208343</v>
+        <v>1.156103599760151</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>19.14353521657862</v>
+        <v>18.08000548232425</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1011130009876434</v>
+        <v>0.1009518240339505</v>
       </c>
       <c r="C20">
-        <v>129.9794770652412</v>
+        <v>128.8486280275893</v>
       </c>
       <c r="D20">
-        <v>131.4494770652412</v>
+        <v>131.8336280275892</v>
       </c>
       <c r="E20">
-        <v>-104.93</v>
+        <v>-103.415</v>
       </c>
       <c r="F20">
-        <v>27.27</v>
+        <v>28.785</v>
       </c>
       <c r="G20">
         <v>25.8</v>
@@ -2921,28 +2921,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M20">
-        <v>1.371681</v>
+        <v>1.4478855</v>
       </c>
       <c r="N20">
-        <v>23.42831900000001</v>
+        <v>23.35211450000001</v>
       </c>
       <c r="O20">
-        <v>4.451380610000002</v>
+        <v>4.436901755000001</v>
       </c>
       <c r="P20">
-        <v>18.97693839000001</v>
+        <v>18.91521274500001</v>
       </c>
       <c r="Q20">
-        <v>37.67693839</v>
+        <v>37.61521274500001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1143649524239553</v>
+        <v>0.1150748815233957</v>
       </c>
       <c r="T20">
-        <v>1.156103599760151</v>
+        <v>1.168074024276202</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.08000548232425</v>
+        <v>17.12842624641245</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1009518240339505</v>
+        <v>0.1007906470802577</v>
       </c>
       <c r="C21">
-        <v>128.8486280275893</v>
+        <v>127.7200308740359</v>
       </c>
       <c r="D21">
-        <v>131.8336280275892</v>
+        <v>132.2200308740359</v>
       </c>
       <c r="E21">
-        <v>-103.415</v>
+        <v>-101.9</v>
       </c>
       <c r="F21">
-        <v>28.785</v>
+        <v>30.3</v>
       </c>
       <c r="G21">
         <v>25.8</v>
@@ -3003,28 +3003,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M21">
-        <v>1.4478855</v>
+        <v>1.52409</v>
       </c>
       <c r="N21">
-        <v>23.35211450000001</v>
+        <v>23.27591000000001</v>
       </c>
       <c r="O21">
-        <v>4.436901755000001</v>
+        <v>4.422422900000002</v>
       </c>
       <c r="P21">
-        <v>18.91521274500001</v>
+        <v>18.85348710000001</v>
       </c>
       <c r="Q21">
-        <v>37.61521274500001</v>
+        <v>37.55348710000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1150748815233957</v>
+        <v>0.1158025588503221</v>
       </c>
       <c r="T21">
-        <v>1.168074024276202</v>
+        <v>1.180343709405153</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.12842624641245</v>
+        <v>16.27200493409183</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1007906470802577</v>
+        <v>0.1006294701265649</v>
       </c>
       <c r="C22">
-        <v>127.7200308740359</v>
+        <v>126.5937054635268</v>
       </c>
       <c r="D22">
-        <v>132.2200308740359</v>
+        <v>132.6087054635268</v>
       </c>
       <c r="E22">
-        <v>-101.9</v>
+        <v>-100.385</v>
       </c>
       <c r="F22">
-        <v>30.3</v>
+        <v>31.815</v>
       </c>
       <c r="G22">
         <v>25.8</v>
@@ -3085,28 +3085,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M22">
-        <v>1.52409</v>
+        <v>1.6002945</v>
       </c>
       <c r="N22">
-        <v>23.27591000000001</v>
+        <v>23.19970550000001</v>
       </c>
       <c r="O22">
-        <v>4.422422900000002</v>
+        <v>4.407944045000002</v>
       </c>
       <c r="P22">
-        <v>18.85348710000001</v>
+        <v>18.79176145500001</v>
       </c>
       <c r="Q22">
-        <v>37.55348710000001</v>
+        <v>37.491761455</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1158025588503221</v>
+        <v>0.1165486583880568</v>
       </c>
       <c r="T22">
-        <v>1.180343709405153</v>
+        <v>1.192924019474078</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.27200493409183</v>
+        <v>15.49714755627793</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1006294701265649</v>
+        <v>0.1004682931728721</v>
       </c>
       <c r="C23">
-        <v>126.5937054635269</v>
+        <v>125.4696718892057</v>
       </c>
       <c r="D23">
-        <v>132.6087054635269</v>
+        <v>132.9996718892057</v>
       </c>
       <c r="E23">
-        <v>-100.385</v>
+        <v>-98.86999999999999</v>
       </c>
       <c r="F23">
-        <v>31.815</v>
+        <v>33.33</v>
       </c>
       <c r="G23">
         <v>25.8</v>
@@ -3167,28 +3167,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M23">
-        <v>1.6002945</v>
+        <v>1.676499</v>
       </c>
       <c r="N23">
-        <v>23.19970550000001</v>
+        <v>23.12350100000001</v>
       </c>
       <c r="O23">
-        <v>4.407944045000002</v>
+        <v>4.393465190000001</v>
       </c>
       <c r="P23">
-        <v>18.79176145500001</v>
+        <v>18.73003581000001</v>
       </c>
       <c r="Q23">
-        <v>37.491761455</v>
+        <v>37.43003581000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1165486583880568</v>
+        <v>0.1173138886831693</v>
       </c>
       <c r="T23">
-        <v>1.192924019474078</v>
+        <v>1.205826901596053</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.49714755627793</v>
+        <v>14.7927317582653</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1004682931728721</v>
+        <v>0.1003071162191793</v>
       </c>
       <c r="C24">
-        <v>125.4696718892057</v>
+        <v>124.3479504818769</v>
       </c>
       <c r="D24">
-        <v>132.9996718892057</v>
+        <v>133.3929504818769</v>
       </c>
       <c r="E24">
-        <v>-98.86999999999999</v>
+        <v>-97.35499999999999</v>
       </c>
       <c r="F24">
-        <v>33.33</v>
+        <v>34.845</v>
       </c>
       <c r="G24">
         <v>25.8</v>
@@ -3249,28 +3249,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M24">
-        <v>1.676499</v>
+        <v>1.7527035</v>
       </c>
       <c r="N24">
-        <v>23.12350100000001</v>
+        <v>23.04729650000001</v>
       </c>
       <c r="O24">
-        <v>4.393465190000001</v>
+        <v>4.378986335000001</v>
       </c>
       <c r="P24">
-        <v>18.73003581000001</v>
+        <v>18.66831016500001</v>
       </c>
       <c r="Q24">
-        <v>37.43003581000001</v>
+        <v>37.36831016500001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1173138886831693</v>
+        <v>0.1180989950898432</v>
       </c>
       <c r="T24">
-        <v>1.205826901596053</v>
+        <v>1.219064923513403</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.7927317582653</v>
+        <v>14.14956950790594</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1003071162191793</v>
+        <v>0.1001459392654865</v>
       </c>
       <c r="C25">
-        <v>124.3479504818769</v>
+        <v>123.2285618135302</v>
       </c>
       <c r="D25">
-        <v>133.3929504818769</v>
+        <v>133.7885618135302</v>
       </c>
       <c r="E25">
-        <v>-97.35499999999999</v>
+        <v>-95.83999999999999</v>
       </c>
       <c r="F25">
-        <v>34.845</v>
+        <v>36.36</v>
       </c>
       <c r="G25">
         <v>25.8</v>
@@ -3331,28 +3331,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M25">
-        <v>1.7527035</v>
+        <v>1.828908</v>
       </c>
       <c r="N25">
-        <v>23.04729650000001</v>
+        <v>22.97109200000001</v>
       </c>
       <c r="O25">
-        <v>4.378986335000001</v>
+        <v>4.364507480000002</v>
       </c>
       <c r="P25">
-        <v>18.66831016500001</v>
+        <v>18.60658452000001</v>
       </c>
       <c r="Q25">
-        <v>37.36831016500001</v>
+        <v>37.30658452</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1180989950898432</v>
+        <v>0.1189047621914295</v>
       </c>
       <c r="T25">
-        <v>1.219064923513403</v>
+        <v>1.232651314428579</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.14956950790594</v>
+        <v>13.56000411174319</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1001459392654865</v>
+        <v>0.09998476231179362</v>
       </c>
       <c r="C26">
-        <v>123.2285618135302</v>
+        <v>122.1115267009272</v>
       </c>
       <c r="D26">
-        <v>133.7885618135302</v>
+        <v>134.1865267009272</v>
       </c>
       <c r="E26">
-        <v>-95.83999999999999</v>
+        <v>-94.32499999999999</v>
       </c>
       <c r="F26">
-        <v>36.36</v>
+        <v>37.875</v>
       </c>
       <c r="G26">
         <v>25.8</v>
@@ -3413,28 +3413,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M26">
-        <v>1.828908</v>
+        <v>1.9051125</v>
       </c>
       <c r="N26">
-        <v>22.97109200000001</v>
+        <v>22.89488750000001</v>
       </c>
       <c r="O26">
-        <v>4.364507480000002</v>
+        <v>4.350028625000001</v>
       </c>
       <c r="P26">
-        <v>18.60658452000001</v>
+        <v>18.54485887500001</v>
       </c>
       <c r="Q26">
-        <v>37.30658452</v>
+        <v>37.24485887500001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1189047621914295</v>
+        <v>0.1197320164157248</v>
       </c>
       <c r="T26">
-        <v>1.232651314428579</v>
+        <v>1.246600009101492</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>13.56000411174319</v>
+        <v>13.01760394727346</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09998476231179362</v>
+        <v>0.1001394853581008</v>
       </c>
       <c r="C27">
-        <v>122.1115267009272</v>
+        <v>120.2144518975365</v>
       </c>
       <c r="D27">
-        <v>134.1865267009272</v>
+        <v>133.8044518975365</v>
       </c>
       <c r="E27">
-        <v>-94.32499999999999</v>
+        <v>-92.80999999999999</v>
       </c>
       <c r="F27">
-        <v>37.875</v>
+        <v>39.39</v>
       </c>
       <c r="G27">
         <v>25.8</v>
@@ -3495,45 +3495,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M27">
-        <v>1.9051125</v>
+        <v>2.040402</v>
       </c>
       <c r="N27">
-        <v>22.89488750000001</v>
+        <v>22.75959800000001</v>
       </c>
       <c r="O27">
-        <v>4.350028625000001</v>
+        <v>4.324323620000001</v>
       </c>
       <c r="P27">
-        <v>18.54485887500001</v>
+        <v>18.43527438000001</v>
       </c>
       <c r="Q27">
-        <v>37.24485887500001</v>
+        <v>37.13527438000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1197320164157248</v>
+        <v>0.1205816288622984</v>
       </c>
       <c r="T27">
-        <v>1.246600009101492</v>
+        <v>1.260925695522323</v>
       </c>
       <c r="U27">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V27">
         <v>0.19</v>
       </c>
       <c r="W27">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y27">
-        <v>13.01760394727346</v>
+        <v>12.15446760001216</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1001394853581008</v>
+        <v>0.09999045840440798</v>
       </c>
       <c r="C28">
-        <v>120.2144518975365</v>
+        <v>119.0674220244548</v>
       </c>
       <c r="D28">
-        <v>133.8044518975365</v>
+        <v>134.1724220244548</v>
       </c>
       <c r="E28">
-        <v>-92.80999999999999</v>
+        <v>-91.29499999999999</v>
       </c>
       <c r="F28">
-        <v>39.39</v>
+        <v>40.905</v>
       </c>
       <c r="G28">
         <v>25.8</v>
@@ -3577,28 +3577,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M28">
-        <v>2.040402</v>
+        <v>2.118879</v>
       </c>
       <c r="N28">
-        <v>22.75959800000001</v>
+        <v>22.68112100000001</v>
       </c>
       <c r="O28">
-        <v>4.324323620000001</v>
+        <v>4.309412990000002</v>
       </c>
       <c r="P28">
-        <v>18.43527438000001</v>
+        <v>18.37170801000001</v>
       </c>
       <c r="Q28">
-        <v>37.13527438000001</v>
+        <v>37.07170801000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1205816288622984</v>
+        <v>0.1214545183622027</v>
       </c>
       <c r="T28">
-        <v>1.260925695522323</v>
+        <v>1.275643866502627</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>12.15446760001216</v>
+        <v>11.70430213334504</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09999045840440798</v>
+        <v>0.09984143145071518</v>
       </c>
       <c r="C29">
-        <v>119.0674220244548</v>
+        <v>117.9224216115702</v>
       </c>
       <c r="D29">
-        <v>134.1724220244548</v>
+        <v>134.5424216115702</v>
       </c>
       <c r="E29">
-        <v>-91.29499999999999</v>
+        <v>-89.77999999999999</v>
       </c>
       <c r="F29">
-        <v>40.905</v>
+        <v>42.42</v>
       </c>
       <c r="G29">
         <v>25.8</v>
@@ -3659,28 +3659,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M29">
-        <v>2.118879</v>
+        <v>2.197356</v>
       </c>
       <c r="N29">
-        <v>22.68112100000001</v>
+        <v>22.60264400000001</v>
       </c>
       <c r="O29">
-        <v>4.309412990000002</v>
+        <v>4.294502360000002</v>
       </c>
       <c r="P29">
-        <v>18.37170801000001</v>
+        <v>18.30814164000001</v>
       </c>
       <c r="Q29">
-        <v>37.07170801000001</v>
+        <v>37.00814164000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1214545183622027</v>
+        <v>0.12235165479266</v>
       </c>
       <c r="T29">
-        <v>1.275643866502627</v>
+        <v>1.290770875565719</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.70430213334504</v>
+        <v>11.28629134286843</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09984143145071518</v>
+        <v>0.09969240449702238</v>
       </c>
       <c r="C30">
-        <v>117.9224216115702</v>
+        <v>116.7794674948882</v>
       </c>
       <c r="D30">
-        <v>134.5424216115702</v>
+        <v>134.9144674948882</v>
       </c>
       <c r="E30">
-        <v>-89.77999999999999</v>
+        <v>-88.26499999999999</v>
       </c>
       <c r="F30">
-        <v>42.42</v>
+        <v>43.935</v>
       </c>
       <c r="G30">
         <v>25.8</v>
@@ -3741,28 +3741,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M30">
-        <v>2.197356</v>
+        <v>2.275833</v>
       </c>
       <c r="N30">
-        <v>22.60264400000001</v>
+        <v>22.52416700000001</v>
       </c>
       <c r="O30">
-        <v>4.294502360000002</v>
+        <v>4.279591730000002</v>
       </c>
       <c r="P30">
-        <v>18.30814164000001</v>
+        <v>18.24457527000001</v>
       </c>
       <c r="Q30">
-        <v>37.00814164000001</v>
+        <v>36.94457527</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.12235165479266</v>
+        <v>0.1232740626718625</v>
       </c>
       <c r="T30">
-        <v>1.290770875565719</v>
+        <v>1.306323997560165</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.28629134286843</v>
+        <v>10.89710888276952</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09969240449702235</v>
+        <v>0.09954337754332954</v>
       </c>
       <c r="C31">
-        <v>116.7794674948882</v>
+        <v>115.6385766971549</v>
       </c>
       <c r="D31">
-        <v>134.9144674948882</v>
+        <v>135.2885766971549</v>
       </c>
       <c r="E31">
-        <v>-88.26499999999999</v>
+        <v>-86.75</v>
       </c>
       <c r="F31">
-        <v>43.935</v>
+        <v>45.45</v>
       </c>
       <c r="G31">
         <v>25.8</v>
@@ -3823,28 +3823,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M31">
-        <v>2.275833</v>
+        <v>2.35431</v>
       </c>
       <c r="N31">
-        <v>22.52416700000001</v>
+        <v>22.44569000000001</v>
       </c>
       <c r="O31">
-        <v>4.279591730000002</v>
+        <v>4.264681100000002</v>
       </c>
       <c r="P31">
-        <v>18.24457527000001</v>
+        <v>18.18100890000001</v>
       </c>
       <c r="Q31">
-        <v>36.94457527</v>
+        <v>36.8810089</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1232740626718625</v>
+        <v>0.1242228250618994</v>
       </c>
       <c r="T31">
-        <v>1.306323997560164</v>
+        <v>1.322321494468737</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.89710888276952</v>
+        <v>10.53387192001054</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09954337754332954</v>
+        <v>0.09939435058963672</v>
       </c>
       <c r="C32">
-        <v>115.6385766971549</v>
+        <v>114.4997664304533</v>
       </c>
       <c r="D32">
-        <v>135.2885766971549</v>
+        <v>135.6647664304533</v>
       </c>
       <c r="E32">
-        <v>-86.75</v>
+        <v>-85.23499999999999</v>
       </c>
       <c r="F32">
-        <v>45.45</v>
+        <v>46.965</v>
       </c>
       <c r="G32">
         <v>25.8</v>
@@ -3905,28 +3905,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M32">
-        <v>2.35431</v>
+        <v>2.432787</v>
       </c>
       <c r="N32">
-        <v>22.44569000000001</v>
+        <v>22.36721300000001</v>
       </c>
       <c r="O32">
-        <v>4.264681100000002</v>
+        <v>4.249770470000001</v>
       </c>
       <c r="P32">
-        <v>18.18100890000001</v>
+        <v>18.11744253000001</v>
       </c>
       <c r="Q32">
-        <v>36.8810089</v>
+        <v>36.81744253000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1242228250618994</v>
+        <v>0.1251990878110677</v>
       </c>
       <c r="T32">
-        <v>1.322321494468737</v>
+        <v>1.338782686939877</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.53387192001054</v>
+        <v>10.1940696000102</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09939435058963672</v>
+        <v>0.09924532363594393</v>
       </c>
       <c r="C33">
-        <v>114.4997664304533</v>
+        <v>113.363054098843</v>
       </c>
       <c r="D33">
-        <v>135.6647664304533</v>
+        <v>136.043054098843</v>
       </c>
       <c r="E33">
-        <v>-85.23499999999999</v>
+        <v>-83.71999999999998</v>
       </c>
       <c r="F33">
-        <v>46.965</v>
+        <v>48.48</v>
       </c>
       <c r="G33">
         <v>25.8</v>
@@ -3987,28 +3987,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M33">
-        <v>2.432787</v>
+        <v>2.511264</v>
       </c>
       <c r="N33">
-        <v>22.36721300000001</v>
+        <v>22.28873600000001</v>
       </c>
       <c r="O33">
-        <v>4.249770470000001</v>
+        <v>4.234859840000001</v>
       </c>
       <c r="P33">
-        <v>18.11744253000001</v>
+        <v>18.05387616000001</v>
       </c>
       <c r="Q33">
-        <v>36.81744253000001</v>
+        <v>36.75387616</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1251990878110677</v>
+        <v>0.1262040641705058</v>
       </c>
       <c r="T33">
-        <v>1.338782686939877</v>
+        <v>1.355728032130757</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.1940696000102</v>
+        <v>9.875504925009878</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09924532363594393</v>
+        <v>0.09955070668225108</v>
       </c>
       <c r="C34">
-        <v>113.363054098843</v>
+        <v>111.075129520656</v>
       </c>
       <c r="D34">
-        <v>136.043054098843</v>
+        <v>135.270129520656</v>
       </c>
       <c r="E34">
-        <v>-83.71999999999998</v>
+        <v>-82.20499999999998</v>
       </c>
       <c r="F34">
-        <v>48.48</v>
+        <v>49.995</v>
       </c>
       <c r="G34">
         <v>25.8</v>
@@ -4069,45 +4069,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M34">
-        <v>2.511264</v>
+        <v>2.6747325</v>
       </c>
       <c r="N34">
-        <v>22.28873600000001</v>
+        <v>22.12526750000001</v>
       </c>
       <c r="O34">
-        <v>4.234859840000001</v>
+        <v>4.203800825000001</v>
       </c>
       <c r="P34">
-        <v>18.05387616000001</v>
+        <v>17.921466675</v>
       </c>
       <c r="Q34">
-        <v>36.75387616</v>
+        <v>36.62146667500001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1262040641705058</v>
+        <v>0.1272390398242554</v>
       </c>
       <c r="T34">
-        <v>1.355728032130757</v>
+        <v>1.373179208521364</v>
       </c>
       <c r="U34">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V34">
         <v>0.19</v>
       </c>
       <c r="W34">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>9.875504925009878</v>
+        <v>9.271955232906469</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09955070668225108</v>
+        <v>0.09941544972855829</v>
       </c>
       <c r="C35">
-        <v>111.075129520656</v>
+        <v>109.9013786519646</v>
       </c>
       <c r="D35">
-        <v>135.270129520656</v>
+        <v>135.6113786519646</v>
       </c>
       <c r="E35">
-        <v>-82.20499999999998</v>
+        <v>-80.68999999999998</v>
       </c>
       <c r="F35">
-        <v>49.995</v>
+        <v>51.51000000000001</v>
       </c>
       <c r="G35">
         <v>25.8</v>
@@ -4151,28 +4151,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M35">
-        <v>2.6747325</v>
+        <v>2.755785</v>
       </c>
       <c r="N35">
-        <v>22.12526750000001</v>
+        <v>22.04421500000001</v>
       </c>
       <c r="O35">
-        <v>4.203800825000001</v>
+        <v>4.188400850000002</v>
       </c>
       <c r="P35">
-        <v>17.921466675</v>
+        <v>17.85581415000001</v>
       </c>
       <c r="Q35">
-        <v>36.62146667500001</v>
+        <v>36.55581415</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1272390398242554</v>
+        <v>0.1283053783766035</v>
       </c>
       <c r="T35">
-        <v>1.373179208521364</v>
+        <v>1.39115920843896</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.271955232906469</v>
+        <v>8.999250667232751</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09941544972855829</v>
+        <v>0.09928019277486547</v>
       </c>
       <c r="C36">
-        <v>109.9013786519646</v>
+        <v>108.729353892158</v>
       </c>
       <c r="D36">
-        <v>135.6113786519646</v>
+        <v>135.954353892158</v>
       </c>
       <c r="E36">
-        <v>-80.68999999999998</v>
+        <v>-79.17499999999998</v>
       </c>
       <c r="F36">
-        <v>51.51000000000001</v>
+        <v>53.02500000000001</v>
       </c>
       <c r="G36">
         <v>25.8</v>
@@ -4233,28 +4233,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M36">
-        <v>2.755785</v>
+        <v>2.8368375</v>
       </c>
       <c r="N36">
-        <v>22.04421500000001</v>
+        <v>21.96316250000001</v>
       </c>
       <c r="O36">
-        <v>4.188400850000002</v>
+        <v>4.173000875000001</v>
       </c>
       <c r="P36">
-        <v>17.85581415000001</v>
+        <v>17.790161625</v>
       </c>
       <c r="Q36">
-        <v>36.55581415</v>
+        <v>36.490161625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1283053783766035</v>
+        <v>0.1294045273459469</v>
       </c>
       <c r="T36">
-        <v>1.39115920843896</v>
+        <v>1.40969243912325</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.999250667232751</v>
+        <v>8.74212921959753</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09928019277486547</v>
+        <v>0.09914493582117265</v>
       </c>
       <c r="C37">
-        <v>108.729353892158</v>
+        <v>107.5590683709676</v>
       </c>
       <c r="D37">
-        <v>135.954353892158</v>
+        <v>136.2990683709676</v>
       </c>
       <c r="E37">
-        <v>-79.17499999999998</v>
+        <v>-77.65999999999998</v>
       </c>
       <c r="F37">
-        <v>53.02500000000001</v>
+        <v>54.54000000000001</v>
       </c>
       <c r="G37">
         <v>25.8</v>
@@ -4315,28 +4315,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M37">
-        <v>2.8368375</v>
+        <v>2.91789</v>
       </c>
       <c r="N37">
-        <v>21.96316250000001</v>
+        <v>21.88211000000001</v>
       </c>
       <c r="O37">
-        <v>4.173000875000001</v>
+        <v>4.157600900000001</v>
       </c>
       <c r="P37">
-        <v>17.790161625</v>
+        <v>17.72450910000001</v>
       </c>
       <c r="Q37">
-        <v>36.490161625</v>
+        <v>36.42450910000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1294045273459469</v>
+        <v>0.1305380247205823</v>
       </c>
       <c r="T37">
-        <v>1.40969243912325</v>
+        <v>1.428804833266425</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.74212921959753</v>
+        <v>8.49929229683093</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09914493582117266</v>
+        <v>0.09900967886747984</v>
       </c>
       <c r="C38">
-        <v>107.5590683709676</v>
+        <v>106.3905353516261</v>
       </c>
       <c r="D38">
-        <v>136.2990683709676</v>
+        <v>136.6455353516261</v>
       </c>
       <c r="E38">
-        <v>-77.66</v>
+        <v>-76.14499999999998</v>
       </c>
       <c r="F38">
-        <v>54.54</v>
+        <v>56.055</v>
       </c>
       <c r="G38">
         <v>25.8</v>
@@ -4397,28 +4397,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M38">
-        <v>2.91789</v>
+        <v>2.9989425</v>
       </c>
       <c r="N38">
-        <v>21.88211000000001</v>
+        <v>21.80105750000001</v>
       </c>
       <c r="O38">
-        <v>4.157600900000001</v>
+        <v>4.142200925000001</v>
       </c>
       <c r="P38">
-        <v>17.72450910000001</v>
+        <v>17.65885657500001</v>
       </c>
       <c r="Q38">
-        <v>36.42450910000001</v>
+        <v>36.358856575</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1305380247205823</v>
+        <v>0.1317075061388569</v>
       </c>
       <c r="T38">
-        <v>1.428804833266425</v>
+        <v>1.448523970080812</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.499292296830932</v>
+        <v>8.26958169421388</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09900967886747984</v>
+        <v>0.09887442191378702</v>
       </c>
       <c r="C39">
-        <v>106.3905353516261</v>
+        <v>105.2237682325685</v>
       </c>
       <c r="D39">
-        <v>136.6455353516261</v>
+        <v>136.9937682325684</v>
       </c>
       <c r="E39">
-        <v>-76.14499999999998</v>
+        <v>-74.63</v>
       </c>
       <c r="F39">
-        <v>56.055</v>
+        <v>57.57</v>
       </c>
       <c r="G39">
         <v>25.8</v>
@@ -4479,28 +4479,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M39">
-        <v>2.9989425</v>
+        <v>3.079995</v>
       </c>
       <c r="N39">
-        <v>21.80105750000001</v>
+        <v>21.72000500000001</v>
       </c>
       <c r="O39">
-        <v>4.142200925000001</v>
+        <v>4.126800950000002</v>
       </c>
       <c r="P39">
-        <v>17.65885657500001</v>
+        <v>17.59320405</v>
       </c>
       <c r="Q39">
-        <v>36.358856575</v>
+        <v>36.29320405</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1317075061388569</v>
+        <v>0.1329147127641726</v>
       </c>
       <c r="T39">
-        <v>1.448523970080812</v>
+        <v>1.46887920808276</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.26958169421388</v>
+        <v>8.051961123313514</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09887442191378702</v>
+        <v>0.0987391649600942</v>
       </c>
       <c r="C40">
-        <v>105.2237682325685</v>
+        <v>104.0587805491587</v>
       </c>
       <c r="D40">
-        <v>136.9937682325684</v>
+        <v>137.3437805491587</v>
       </c>
       <c r="E40">
-        <v>-74.63</v>
+        <v>-73.11499999999998</v>
       </c>
       <c r="F40">
-        <v>57.57</v>
+        <v>59.085</v>
       </c>
       <c r="G40">
         <v>25.8</v>
@@ -4561,28 +4561,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M40">
-        <v>3.079995</v>
+        <v>3.1610475</v>
       </c>
       <c r="N40">
-        <v>21.72000500000001</v>
+        <v>21.63895250000001</v>
       </c>
       <c r="O40">
-        <v>4.126800950000002</v>
+        <v>4.111400975000001</v>
       </c>
       <c r="P40">
-        <v>17.59320405</v>
+        <v>17.52755152500001</v>
       </c>
       <c r="Q40">
-        <v>36.29320405</v>
+        <v>36.22755152500001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1329147127641726</v>
+        <v>0.1341614999345807</v>
       </c>
       <c r="T40">
-        <v>1.46887920808276</v>
+        <v>1.48990183093723</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.051961123313514</v>
+        <v>7.845500581690091</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0987391649600942</v>
+        <v>0.09860390800640137</v>
       </c>
       <c r="C41">
-        <v>104.0587805491587</v>
+        <v>102.8955859754443</v>
       </c>
       <c r="D41">
-        <v>137.3437805491587</v>
+        <v>137.6955859754443</v>
       </c>
       <c r="E41">
-        <v>-73.11499999999998</v>
+        <v>-71.59999999999999</v>
       </c>
       <c r="F41">
-        <v>59.085</v>
+        <v>60.6</v>
       </c>
       <c r="G41">
         <v>25.8</v>
@@ -4643,28 +4643,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M41">
-        <v>3.1610475</v>
+        <v>3.2421</v>
       </c>
       <c r="N41">
-        <v>21.63895250000001</v>
+        <v>21.55790000000001</v>
       </c>
       <c r="O41">
-        <v>4.111400975000001</v>
+        <v>4.096001000000001</v>
       </c>
       <c r="P41">
-        <v>17.52755152500001</v>
+        <v>17.46189900000001</v>
       </c>
       <c r="Q41">
-        <v>36.22755152500001</v>
+        <v>36.16189900000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1341614999345807</v>
+        <v>0.1354498466773356</v>
       </c>
       <c r="T41">
-        <v>1.48990183093723</v>
+        <v>1.511625207886849</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.845500581690091</v>
+        <v>7.649363067147838</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09860390800640137</v>
+        <v>0.09873433105270857</v>
       </c>
       <c r="C42">
-        <v>102.8955859754443</v>
+        <v>101.0413226386111</v>
       </c>
       <c r="D42">
-        <v>137.6955859754443</v>
+        <v>137.3563226386111</v>
       </c>
       <c r="E42">
-        <v>-71.59999999999999</v>
+        <v>-70.08499999999998</v>
       </c>
       <c r="F42">
-        <v>60.6</v>
+        <v>62.115</v>
       </c>
       <c r="G42">
         <v>25.8</v>
@@ -4725,45 +4725,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M42">
-        <v>3.2421</v>
+        <v>3.3728445</v>
       </c>
       <c r="N42">
-        <v>21.55790000000001</v>
+        <v>21.42715550000001</v>
       </c>
       <c r="O42">
-        <v>4.096001000000001</v>
+        <v>4.071159545000001</v>
       </c>
       <c r="P42">
-        <v>17.46189900000001</v>
+        <v>17.35599595500001</v>
       </c>
       <c r="Q42">
-        <v>36.16189900000001</v>
+        <v>36.05599595500001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1354498466773356</v>
+        <v>0.1367818661910315</v>
       </c>
       <c r="T42">
-        <v>1.511625207886849</v>
+        <v>1.534084970495778</v>
       </c>
       <c r="U42">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V42">
         <v>0.19</v>
       </c>
       <c r="W42">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y42">
-        <v>7.649363067147838</v>
+        <v>7.352844164621288</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09873433105270857</v>
+        <v>0.09860555409901575</v>
       </c>
       <c r="C43">
-        <v>101.0413226386111</v>
+        <v>99.86129362985727</v>
       </c>
       <c r="D43">
-        <v>137.3563226386111</v>
+        <v>137.6912936298573</v>
       </c>
       <c r="E43">
-        <v>-70.08499999999998</v>
+        <v>-68.56999999999999</v>
       </c>
       <c r="F43">
-        <v>62.115</v>
+        <v>63.63</v>
       </c>
       <c r="G43">
         <v>25.8</v>
@@ -4807,28 +4807,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M43">
-        <v>3.3728445</v>
+        <v>3.455109</v>
       </c>
       <c r="N43">
-        <v>21.42715550000001</v>
+        <v>21.34489100000001</v>
       </c>
       <c r="O43">
-        <v>4.071159545000001</v>
+        <v>4.055529290000002</v>
       </c>
       <c r="P43">
-        <v>17.35599595500001</v>
+        <v>17.28936171</v>
       </c>
       <c r="Q43">
-        <v>36.05599595500001</v>
+        <v>35.98936171</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1367818661910315</v>
+        <v>0.1381598174120961</v>
       </c>
       <c r="T43">
-        <v>1.534084970495778</v>
+        <v>1.557319207677428</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.352844164621288</v>
+        <v>7.177776446416019</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09860555409901575</v>
+        <v>0.09847677714532292</v>
       </c>
       <c r="C44">
-        <v>99.86129362985727</v>
+        <v>98.68290240329763</v>
       </c>
       <c r="D44">
-        <v>137.6912936298573</v>
+        <v>138.0279024032976</v>
       </c>
       <c r="E44">
-        <v>-68.56999999999999</v>
+        <v>-67.05499999999999</v>
       </c>
       <c r="F44">
-        <v>63.63</v>
+        <v>65.145</v>
       </c>
       <c r="G44">
         <v>25.8</v>
@@ -4889,28 +4889,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M44">
-        <v>3.455109</v>
+        <v>3.5373735</v>
       </c>
       <c r="N44">
-        <v>21.34489100000001</v>
+        <v>21.26262650000001</v>
       </c>
       <c r="O44">
-        <v>4.055529290000002</v>
+        <v>4.039899035000001</v>
       </c>
       <c r="P44">
-        <v>17.28936171</v>
+        <v>17.22272746500001</v>
       </c>
       <c r="Q44">
-        <v>35.98936171</v>
+        <v>35.92272746500001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1381598174120961</v>
+        <v>0.1395861177988121</v>
       </c>
       <c r="T44">
-        <v>1.557319207677428</v>
+        <v>1.581368681251416</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.17777644641602</v>
+        <v>7.010851412778438</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09847677714532292</v>
+        <v>0.09834800019163012</v>
       </c>
       <c r="C45">
-        <v>98.68290240329763</v>
+        <v>97.50616099984333</v>
       </c>
       <c r="D45">
-        <v>138.0279024032976</v>
+        <v>138.3661609998433</v>
       </c>
       <c r="E45">
-        <v>-67.05499999999999</v>
+        <v>-65.53999999999999</v>
       </c>
       <c r="F45">
-        <v>65.145</v>
+        <v>66.66</v>
       </c>
       <c r="G45">
         <v>25.8</v>
@@ -4971,28 +4971,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M45">
-        <v>3.5373735</v>
+        <v>3.619638</v>
       </c>
       <c r="N45">
-        <v>21.26262650000001</v>
+        <v>21.18036200000001</v>
       </c>
       <c r="O45">
-        <v>4.039899035000001</v>
+        <v>4.024268780000002</v>
       </c>
       <c r="P45">
-        <v>17.22272746500001</v>
+        <v>17.15609322000001</v>
       </c>
       <c r="Q45">
-        <v>35.92272746500001</v>
+        <v>35.85609322000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1395861177988121</v>
+        <v>0.1410633574850538</v>
       </c>
       <c r="T45">
-        <v>1.581368681251416</v>
+        <v>1.606277064595905</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.010851412778438</v>
+        <v>6.851513880669838</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09834800019163012</v>
+        <v>0.0982192232379373</v>
       </c>
       <c r="C46">
-        <v>97.50616099984333</v>
+        <v>96.3310815787281</v>
       </c>
       <c r="D46">
-        <v>138.3661609998433</v>
+        <v>138.7060815787281</v>
       </c>
       <c r="E46">
-        <v>-65.53999999999999</v>
+        <v>-64.02499999999999</v>
       </c>
       <c r="F46">
-        <v>66.66</v>
+        <v>68.175</v>
       </c>
       <c r="G46">
         <v>25.8</v>
@@ -5053,28 +5053,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M46">
-        <v>3.619638</v>
+        <v>3.7019025</v>
       </c>
       <c r="N46">
-        <v>21.18036200000001</v>
+        <v>21.09809750000001</v>
       </c>
       <c r="O46">
-        <v>4.024268780000002</v>
+        <v>4.008638525000002</v>
       </c>
       <c r="P46">
-        <v>17.15609322000001</v>
+        <v>17.08945897500001</v>
       </c>
       <c r="Q46">
-        <v>35.85609322000001</v>
+        <v>35.789458975</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1410633574850538</v>
+        <v>0.1425943149780678</v>
       </c>
       <c r="T46">
-        <v>1.606277064595905</v>
+        <v>1.632091207334738</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.851513880669838</v>
+        <v>6.699258016654952</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0982192232379373</v>
+        <v>0.09809044628424449</v>
       </c>
       <c r="C47">
-        <v>96.3310815787281</v>
+        <v>95.15767641896485</v>
       </c>
       <c r="D47">
-        <v>138.7060815787281</v>
+        <v>139.0476764189648</v>
       </c>
       <c r="E47">
-        <v>-64.02499999999999</v>
+        <v>-62.50999999999999</v>
       </c>
       <c r="F47">
-        <v>68.175</v>
+        <v>69.69</v>
       </c>
       <c r="G47">
         <v>25.8</v>
@@ -5135,28 +5135,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M47">
-        <v>3.7019025</v>
+        <v>3.784167</v>
       </c>
       <c r="N47">
-        <v>21.09809750000001</v>
+        <v>21.01583300000001</v>
       </c>
       <c r="O47">
-        <v>4.008638525000002</v>
+        <v>3.993008270000002</v>
       </c>
       <c r="P47">
-        <v>17.08945897500001</v>
+        <v>17.02282473000001</v>
       </c>
       <c r="Q47">
-        <v>35.789458975</v>
+        <v>35.72282473000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1425943149780678</v>
+        <v>0.1441819746004527</v>
       </c>
       <c r="T47">
-        <v>1.632091207334738</v>
+        <v>1.658861429434269</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.699258016654952</v>
+        <v>6.553621972814627</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09809044628424449</v>
+        <v>0.09796166933055167</v>
       </c>
       <c r="C48">
-        <v>95.15767641896485</v>
+        <v>93.98595792082453</v>
       </c>
       <c r="D48">
-        <v>139.0476764189648</v>
+        <v>139.3909579208245</v>
       </c>
       <c r="E48">
-        <v>-62.50999999999999</v>
+        <v>-60.99499999999999</v>
       </c>
       <c r="F48">
-        <v>69.69</v>
+        <v>71.205</v>
       </c>
       <c r="G48">
         <v>25.8</v>
@@ -5217,28 +5217,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M48">
-        <v>3.784167</v>
+        <v>3.8664315</v>
       </c>
       <c r="N48">
-        <v>21.01583300000001</v>
+        <v>20.93356850000001</v>
       </c>
       <c r="O48">
-        <v>3.993008270000002</v>
+        <v>3.977378015000002</v>
       </c>
       <c r="P48">
-        <v>17.02282473000001</v>
+        <v>16.956190485</v>
       </c>
       <c r="Q48">
-        <v>35.72282473000001</v>
+        <v>35.656190485</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1441819746004527</v>
+        <v>0.1458295459067012</v>
       </c>
       <c r="T48">
-        <v>1.658861429434269</v>
+        <v>1.68664184859416</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.553621972814627</v>
+        <v>6.414183207435592</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09796166933055167</v>
+        <v>0.09783289237685887</v>
       </c>
       <c r="C49">
-        <v>93.98595792082453</v>
+        <v>92.81593860733636</v>
       </c>
       <c r="D49">
-        <v>139.3909579208245</v>
+        <v>139.7359386073364</v>
       </c>
       <c r="E49">
-        <v>-60.99499999999999</v>
+        <v>-59.47999999999999</v>
       </c>
       <c r="F49">
-        <v>71.205</v>
+        <v>72.72</v>
       </c>
       <c r="G49">
         <v>25.8</v>
@@ -5299,28 +5299,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M49">
-        <v>3.8664315</v>
+        <v>3.948696</v>
       </c>
       <c r="N49">
-        <v>20.93356850000001</v>
+        <v>20.85130400000001</v>
       </c>
       <c r="O49">
-        <v>3.977378015000002</v>
+        <v>3.961747760000001</v>
       </c>
       <c r="P49">
-        <v>16.956190485</v>
+        <v>16.88955624</v>
       </c>
       <c r="Q49">
-        <v>35.656190485</v>
+        <v>35.58955624000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1458295459067012</v>
+        <v>0.1475404853401132</v>
       </c>
       <c r="T49">
-        <v>1.68664184859416</v>
+        <v>1.715490745414047</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.414183207435592</v>
+        <v>6.280554390614017</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09783289237685885</v>
+        <v>0.09770411542316604</v>
       </c>
       <c r="C50">
-        <v>92.81593860733639</v>
+        <v>91.64763112581112</v>
       </c>
       <c r="D50">
-        <v>139.7359386073364</v>
+        <v>140.0826311258111</v>
       </c>
       <c r="E50">
-        <v>-59.47999999999999</v>
+        <v>-57.96499999999999</v>
       </c>
       <c r="F50">
-        <v>72.72</v>
+        <v>74.235</v>
       </c>
       <c r="G50">
         <v>25.8</v>
@@ -5381,28 +5381,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M50">
-        <v>3.948696</v>
+        <v>4.0309605</v>
       </c>
       <c r="N50">
-        <v>20.85130400000001</v>
+        <v>20.76903950000001</v>
       </c>
       <c r="O50">
-        <v>3.961747760000001</v>
+        <v>3.946117505000002</v>
       </c>
       <c r="P50">
-        <v>16.88955624</v>
+        <v>16.82292199500001</v>
       </c>
       <c r="Q50">
-        <v>35.58955624000001</v>
+        <v>35.522921995</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1475404853401132</v>
+        <v>0.1493185204375805</v>
       </c>
       <c r="T50">
-        <v>1.715490745414046</v>
+        <v>1.745470971520988</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.280554390614017</v>
+        <v>6.152379811213732</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09770411542316604</v>
+        <v>0.09798033846947321</v>
       </c>
       <c r="C51">
-        <v>91.64763112581112</v>
+        <v>89.39108647050128</v>
       </c>
       <c r="D51">
-        <v>140.0826311258111</v>
+        <v>139.3410864705013</v>
       </c>
       <c r="E51">
-        <v>-57.96499999999999</v>
+        <v>-56.44999999999999</v>
       </c>
       <c r="F51">
-        <v>74.235</v>
+        <v>75.75</v>
       </c>
       <c r="G51">
         <v>25.8</v>
@@ -5463,45 +5463,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M51">
-        <v>4.0309605</v>
+        <v>4.188975</v>
       </c>
       <c r="N51">
-        <v>20.76903950000001</v>
+        <v>20.61102500000001</v>
       </c>
       <c r="O51">
-        <v>3.946117505000002</v>
+        <v>3.916094750000002</v>
       </c>
       <c r="P51">
-        <v>16.82292199500001</v>
+        <v>16.69493025000001</v>
       </c>
       <c r="Q51">
-        <v>35.522921995</v>
+        <v>35.39493025</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1493185204375805</v>
+        <v>0.1511676769389464</v>
       </c>
       <c r="T51">
-        <v>1.745470971520988</v>
+        <v>1.776650406672206</v>
       </c>
       <c r="U51">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>6.152379811213732</v>
+        <v>5.920302699347694</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09798033846947321</v>
+        <v>0.09785966151578041</v>
       </c>
       <c r="C52">
-        <v>89.39108647050128</v>
+        <v>88.1990862240515</v>
       </c>
       <c r="D52">
-        <v>139.3410864705013</v>
+        <v>139.6640862240515</v>
       </c>
       <c r="E52">
-        <v>-56.44999999999999</v>
+        <v>-54.93499999999999</v>
       </c>
       <c r="F52">
-        <v>75.75</v>
+        <v>77.265</v>
       </c>
       <c r="G52">
         <v>25.8</v>
@@ -5545,28 +5545,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M52">
-        <v>4.188975</v>
+        <v>4.2727545</v>
       </c>
       <c r="N52">
-        <v>20.61102500000001</v>
+        <v>20.52724550000001</v>
       </c>
       <c r="O52">
-        <v>3.916094750000002</v>
+        <v>3.900176645000001</v>
       </c>
       <c r="P52">
-        <v>16.69493025000001</v>
+        <v>16.627068855</v>
       </c>
       <c r="Q52">
-        <v>35.39493025</v>
+        <v>35.32706885500001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1511676769389464</v>
+        <v>0.1530923092158784</v>
       </c>
       <c r="T52">
-        <v>1.776650406672206</v>
+        <v>1.809102471829597</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.920302699347694</v>
+        <v>5.804218332693817</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09785966151578041</v>
+        <v>0.0977389845620876</v>
       </c>
       <c r="C53">
-        <v>88.1990862240515</v>
+        <v>87.00858691669907</v>
       </c>
       <c r="D53">
-        <v>139.6640862240515</v>
+        <v>139.9885869166991</v>
       </c>
       <c r="E53">
-        <v>-54.93499999999999</v>
+        <v>-53.41999999999999</v>
       </c>
       <c r="F53">
-        <v>77.265</v>
+        <v>78.78</v>
       </c>
       <c r="G53">
         <v>25.8</v>
@@ -5627,28 +5627,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M53">
-        <v>4.2727545</v>
+        <v>4.356534</v>
       </c>
       <c r="N53">
-        <v>20.52724550000001</v>
+        <v>20.44346600000001</v>
       </c>
       <c r="O53">
-        <v>3.900176645000001</v>
+        <v>3.884258540000002</v>
       </c>
       <c r="P53">
-        <v>16.627068855</v>
+        <v>16.55920746000001</v>
       </c>
       <c r="Q53">
-        <v>35.32706885500001</v>
+        <v>35.25920746000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1530923092158784</v>
+        <v>0.1550971345043491</v>
       </c>
       <c r="T53">
-        <v>1.809102471829597</v>
+        <v>1.842906706368545</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.804218332693817</v>
+        <v>5.692598749372783</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0977389845620876</v>
+        <v>0.09761830760839477</v>
       </c>
       <c r="C54">
-        <v>87.00858691669907</v>
+        <v>85.81959903482034</v>
       </c>
       <c r="D54">
-        <v>139.9885869166991</v>
+        <v>140.3145990348203</v>
       </c>
       <c r="E54">
-        <v>-53.41999999999999</v>
+        <v>-51.90499999999999</v>
       </c>
       <c r="F54">
-        <v>78.78</v>
+        <v>80.295</v>
       </c>
       <c r="G54">
         <v>25.8</v>
@@ -5709,28 +5709,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M54">
-        <v>4.356534</v>
+        <v>4.4403135</v>
       </c>
       <c r="N54">
-        <v>20.44346600000001</v>
+        <v>20.35968650000001</v>
       </c>
       <c r="O54">
-        <v>3.884258540000002</v>
+        <v>3.868340435000002</v>
       </c>
       <c r="P54">
-        <v>16.55920746000001</v>
+        <v>16.49134606500001</v>
       </c>
       <c r="Q54">
-        <v>35.25920746000001</v>
+        <v>35.191346065</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1550971345043491</v>
+        <v>0.1571872715072229</v>
       </c>
       <c r="T54">
-        <v>1.842906706368545</v>
+        <v>1.878149418972981</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.692598749372783</v>
+        <v>5.585191225799711</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09761830760839477</v>
+        <v>0.09749763065470196</v>
       </c>
       <c r="C55">
-        <v>85.81959903482034</v>
+        <v>84.63213316270418</v>
       </c>
       <c r="D55">
-        <v>140.3145990348203</v>
+        <v>140.6421331627042</v>
       </c>
       <c r="E55">
-        <v>-51.90499999999999</v>
+        <v>-50.38999999999999</v>
       </c>
       <c r="F55">
-        <v>80.295</v>
+        <v>81.81</v>
       </c>
       <c r="G55">
         <v>25.8</v>
@@ -5791,28 +5791,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M55">
-        <v>4.4403135</v>
+        <v>4.524093000000001</v>
       </c>
       <c r="N55">
-        <v>20.35968650000001</v>
+        <v>20.27590700000001</v>
       </c>
       <c r="O55">
-        <v>3.868340435000002</v>
+        <v>3.852422330000001</v>
       </c>
       <c r="P55">
-        <v>16.49134606500001</v>
+        <v>16.42348467000001</v>
       </c>
       <c r="Q55">
-        <v>35.191346065</v>
+        <v>35.12348467000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1571872715072229</v>
+        <v>0.1593682840319608</v>
       </c>
       <c r="T55">
-        <v>1.878149418972981</v>
+        <v>1.914924423429783</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.585191225799711</v>
+        <v>5.481761758655272</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09749763065470196</v>
+        <v>0.09737695370100914</v>
       </c>
       <c r="C56">
-        <v>84.63213316270418</v>
+        <v>83.44619998369798</v>
       </c>
       <c r="D56">
-        <v>140.6421331627042</v>
+        <v>140.971199983698</v>
       </c>
       <c r="E56">
-        <v>-50.38999999999999</v>
+        <v>-48.87499999999999</v>
       </c>
       <c r="F56">
-        <v>81.81</v>
+        <v>83.325</v>
       </c>
       <c r="G56">
         <v>25.8</v>
@@ -5873,28 +5873,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M56">
-        <v>4.524093000000001</v>
+        <v>4.6078725</v>
       </c>
       <c r="N56">
-        <v>20.27590700000001</v>
+        <v>20.19212750000001</v>
       </c>
       <c r="O56">
-        <v>3.852422330000001</v>
+        <v>3.836504225000002</v>
       </c>
       <c r="P56">
-        <v>16.42348467000001</v>
+        <v>16.35562327500001</v>
       </c>
       <c r="Q56">
-        <v>35.12348467000001</v>
+        <v>35.055623275</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1593682840319608</v>
+        <v>0.161646230446687</v>
       </c>
       <c r="T56">
-        <v>1.914924423429783</v>
+        <v>1.953333872529111</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.481761758655272</v>
+        <v>5.382093363043358</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09737695370100914</v>
+        <v>0.09725627674731632</v>
       </c>
       <c r="C57">
-        <v>83.44619998369798</v>
+        <v>82.26181028136861</v>
       </c>
       <c r="D57">
-        <v>140.971199983698</v>
+        <v>141.3018102813686</v>
       </c>
       <c r="E57">
-        <v>-48.87499999999999</v>
+        <v>-47.35999999999999</v>
       </c>
       <c r="F57">
-        <v>83.325</v>
+        <v>84.84</v>
       </c>
       <c r="G57">
         <v>25.8</v>
@@ -5955,28 +5955,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M57">
-        <v>4.6078725</v>
+        <v>4.691652</v>
       </c>
       <c r="N57">
-        <v>20.19212750000001</v>
+        <v>20.10834800000001</v>
       </c>
       <c r="O57">
-        <v>3.836504225000002</v>
+        <v>3.820586120000001</v>
       </c>
       <c r="P57">
-        <v>16.35562327500001</v>
+        <v>16.28776188000001</v>
       </c>
       <c r="Q57">
-        <v>35.055623275</v>
+        <v>34.98776188000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.161646230446687</v>
+        <v>0.1640277198802644</v>
       </c>
       <c r="T57">
-        <v>1.953333872529111</v>
+        <v>1.993489205678407</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.382093363043358</v>
+        <v>5.285984552989012</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09725627674731632</v>
+        <v>0.0971355997936235</v>
       </c>
       <c r="C58">
-        <v>82.26181028136861</v>
+        <v>81.07897494068082</v>
       </c>
       <c r="D58">
-        <v>141.3018102813686</v>
+        <v>141.6339749406808</v>
       </c>
       <c r="E58">
-        <v>-47.35999999999999</v>
+        <v>-45.84499999999998</v>
       </c>
       <c r="F58">
-        <v>84.84</v>
+        <v>86.355</v>
       </c>
       <c r="G58">
         <v>25.8</v>
@@ -6037,28 +6037,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M58">
-        <v>4.691652</v>
+        <v>4.775431500000001</v>
       </c>
       <c r="N58">
-        <v>20.10834800000001</v>
+        <v>20.02456850000001</v>
       </c>
       <c r="O58">
-        <v>3.820586120000001</v>
+        <v>3.804668015000002</v>
       </c>
       <c r="P58">
-        <v>16.28776188000001</v>
+        <v>16.21990048500001</v>
       </c>
       <c r="Q58">
-        <v>34.98776188000001</v>
+        <v>34.91990048500001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1640277198802644</v>
+        <v>0.1665199762642407</v>
       </c>
       <c r="T58">
-        <v>1.993489205678407</v>
+        <v>2.035512228741624</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.285984552989012</v>
+        <v>5.193247981883942</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0971355997936235</v>
+        <v>0.09701492283993068</v>
       </c>
       <c r="C59">
-        <v>81.07897494068082</v>
+        <v>79.89770494919156</v>
       </c>
       <c r="D59">
-        <v>141.6339749406808</v>
+        <v>141.9677049491916</v>
       </c>
       <c r="E59">
-        <v>-45.84499999999998</v>
+        <v>-44.32999999999998</v>
       </c>
       <c r="F59">
-        <v>86.355</v>
+        <v>87.87</v>
       </c>
       <c r="G59">
         <v>25.8</v>
@@ -6119,28 +6119,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M59">
-        <v>4.775431500000001</v>
+        <v>4.859211</v>
       </c>
       <c r="N59">
-        <v>20.02456850000001</v>
+        <v>19.94078900000001</v>
       </c>
       <c r="O59">
-        <v>3.804668015000002</v>
+        <v>3.788749910000002</v>
       </c>
       <c r="P59">
-        <v>16.21990048500001</v>
+        <v>16.15203909000001</v>
       </c>
       <c r="Q59">
-        <v>34.91990048500001</v>
+        <v>34.85203909000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1665199762642407</v>
+        <v>0.1691309115236445</v>
       </c>
       <c r="T59">
-        <v>2.035512228741624</v>
+        <v>2.079536348141185</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.193247981883942</v>
+        <v>5.103709223575598</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0970149228399307</v>
+        <v>0.09689424588623788</v>
       </c>
       <c r="C60">
-        <v>79.89770494919152</v>
+        <v>78.71801139826164</v>
       </c>
       <c r="D60">
-        <v>141.9677049491915</v>
+        <v>142.3030113982616</v>
       </c>
       <c r="E60">
-        <v>-44.33</v>
+        <v>-42.815</v>
       </c>
       <c r="F60">
-        <v>87.86999999999999</v>
+        <v>89.38499999999999</v>
       </c>
       <c r="G60">
         <v>25.8</v>
@@ -6201,28 +6201,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M60">
-        <v>4.859210999999999</v>
+        <v>4.9429905</v>
       </c>
       <c r="N60">
-        <v>19.94078900000001</v>
+        <v>19.85700950000001</v>
       </c>
       <c r="O60">
-        <v>3.788749910000002</v>
+        <v>3.772831805000001</v>
       </c>
       <c r="P60">
-        <v>16.15203909000001</v>
+        <v>16.084177695</v>
       </c>
       <c r="Q60">
-        <v>34.85203909000001</v>
+        <v>34.784177695</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1691309115236445</v>
+        <v>0.1718692094786289</v>
       </c>
       <c r="T60">
-        <v>2.079536348141185</v>
+        <v>2.125707985560236</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.103709223575599</v>
+        <v>5.0172056774133</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09689424588623788</v>
+        <v>0.09677356893254506</v>
       </c>
       <c r="C61">
-        <v>78.71801139826164</v>
+        <v>77.53990548428457</v>
       </c>
       <c r="D61">
-        <v>142.3030113982616</v>
+        <v>142.6399054842846</v>
       </c>
       <c r="E61">
-        <v>-42.815</v>
+        <v>-41.3</v>
       </c>
       <c r="F61">
-        <v>89.38499999999999</v>
+        <v>90.89999999999999</v>
       </c>
       <c r="G61">
         <v>25.8</v>
@@ -6283,28 +6283,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M61">
-        <v>4.9429905</v>
+        <v>5.02677</v>
       </c>
       <c r="N61">
-        <v>19.85700950000001</v>
+        <v>19.77323000000001</v>
       </c>
       <c r="O61">
-        <v>3.772831805000001</v>
+        <v>3.756913700000002</v>
       </c>
       <c r="P61">
-        <v>16.084177695</v>
+        <v>16.01631630000001</v>
       </c>
       <c r="Q61">
-        <v>34.784177695</v>
+        <v>34.7163163</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1718692094786289</v>
+        <v>0.1747444223313626</v>
       </c>
       <c r="T61">
-        <v>2.125707985560236</v>
+        <v>2.174188204850241</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.0172056774133</v>
+        <v>4.933585582789746</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09677356893254506</v>
+        <v>0.09665289197885224</v>
       </c>
       <c r="C62">
-        <v>77.53990548428457</v>
+        <v>76.36339850993264</v>
       </c>
       <c r="D62">
-        <v>142.6399054842846</v>
+        <v>142.9783985099326</v>
       </c>
       <c r="E62">
-        <v>-41.3</v>
+        <v>-39.785</v>
       </c>
       <c r="F62">
-        <v>90.89999999999999</v>
+        <v>92.41499999999999</v>
       </c>
       <c r="G62">
         <v>25.8</v>
@@ -6365,28 +6365,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M62">
-        <v>5.02677</v>
+        <v>5.110549499999999</v>
       </c>
       <c r="N62">
-        <v>19.77323000000001</v>
+        <v>19.68945050000001</v>
       </c>
       <c r="O62">
-        <v>3.756913700000002</v>
+        <v>3.740995595000001</v>
       </c>
       <c r="P62">
-        <v>16.01631630000001</v>
+        <v>15.94845490500001</v>
       </c>
       <c r="Q62">
-        <v>34.7163163</v>
+        <v>34.64845490500001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1747444223313626</v>
+        <v>0.177767081997057</v>
       </c>
       <c r="T62">
-        <v>2.174188204850241</v>
+        <v>2.22515458923204</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.933585582789746</v>
+        <v>4.852707130612865</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09665289197885224</v>
+        <v>0.09653221502515942</v>
       </c>
       <c r="C63">
-        <v>76.36339850993264</v>
+        <v>75.18850188542096</v>
       </c>
       <c r="D63">
-        <v>142.9783985099326</v>
+        <v>143.3185018854209</v>
       </c>
       <c r="E63">
-        <v>-39.785</v>
+        <v>-38.27</v>
       </c>
       <c r="F63">
-        <v>92.41499999999999</v>
+        <v>93.92999999999999</v>
       </c>
       <c r="G63">
         <v>25.8</v>
@@ -6447,28 +6447,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M63">
-        <v>5.110549499999999</v>
+        <v>5.194329</v>
       </c>
       <c r="N63">
-        <v>19.68945050000001</v>
+        <v>19.60567100000001</v>
       </c>
       <c r="O63">
-        <v>3.740995595000001</v>
+        <v>3.725077490000002</v>
       </c>
       <c r="P63">
-        <v>15.94845490500001</v>
+        <v>15.88059351000001</v>
       </c>
       <c r="Q63">
-        <v>34.64845490500001</v>
+        <v>34.58059351000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.177767081997057</v>
+        <v>0.1809488290135774</v>
       </c>
       <c r="T63">
-        <v>2.22515458923204</v>
+        <v>2.278803414897092</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.852707130612865</v>
+        <v>4.77443766076427</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09653221502515942</v>
+        <v>0.0964115380714666</v>
       </c>
       <c r="C64">
-        <v>75.18850188542096</v>
+        <v>74.01522712978969</v>
       </c>
       <c r="D64">
-        <v>143.3185018854209</v>
+        <v>143.6602271297897</v>
       </c>
       <c r="E64">
-        <v>-38.27</v>
+        <v>-36.75499999999998</v>
       </c>
       <c r="F64">
-        <v>93.92999999999999</v>
+        <v>95.44500000000001</v>
       </c>
       <c r="G64">
         <v>25.8</v>
@@ -6529,28 +6529,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M64">
-        <v>5.194329</v>
+        <v>5.278108500000001</v>
       </c>
       <c r="N64">
-        <v>19.60567100000001</v>
+        <v>19.52189150000001</v>
       </c>
       <c r="O64">
-        <v>3.725077490000002</v>
+        <v>3.709159385000001</v>
       </c>
       <c r="P64">
-        <v>15.88059351000001</v>
+        <v>15.812732115</v>
       </c>
       <c r="Q64">
-        <v>34.58059351000001</v>
+        <v>34.51273211500001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1809488290135774</v>
+        <v>0.1843025623553151</v>
       </c>
       <c r="T64">
-        <v>2.278803414897092</v>
+        <v>2.335352177084579</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.77443766076427</v>
+        <v>4.698652935990232</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0964115380714666</v>
+        <v>0.0962908611177738</v>
       </c>
       <c r="C65">
-        <v>74.01522712978969</v>
+        <v>72.8435858722045</v>
       </c>
       <c r="D65">
-        <v>143.6602271297897</v>
+        <v>144.0035858722045</v>
       </c>
       <c r="E65">
-        <v>-36.75499999999998</v>
+        <v>-35.23999999999998</v>
       </c>
       <c r="F65">
-        <v>95.44500000000001</v>
+        <v>96.96000000000001</v>
       </c>
       <c r="G65">
         <v>25.8</v>
@@ -6611,28 +6611,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M65">
-        <v>5.278108500000001</v>
+        <v>5.361888</v>
       </c>
       <c r="N65">
-        <v>19.52189150000001</v>
+        <v>19.43811200000001</v>
       </c>
       <c r="O65">
-        <v>3.709159385000001</v>
+        <v>3.693241280000001</v>
       </c>
       <c r="P65">
-        <v>15.812732115</v>
+        <v>15.74487072000001</v>
       </c>
       <c r="Q65">
-        <v>34.51273211500001</v>
+        <v>34.44487072</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1843025623553151</v>
+        <v>0.1878426142160383</v>
       </c>
       <c r="T65">
-        <v>2.335352177084579</v>
+        <v>2.395042537171372</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.698652935990232</v>
+        <v>4.625236483865386</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0962908611177738</v>
+        <v>0.09617018416408096</v>
       </c>
       <c r="C66">
-        <v>72.8435858722045</v>
+        <v>71.6735898532758</v>
       </c>
       <c r="D66">
-        <v>144.0035858722045</v>
+        <v>144.3485898532758</v>
       </c>
       <c r="E66">
-        <v>-35.23999999999998</v>
+        <v>-33.72499999999998</v>
       </c>
       <c r="F66">
-        <v>96.96000000000001</v>
+        <v>98.47500000000001</v>
       </c>
       <c r="G66">
         <v>25.8</v>
@@ -6693,28 +6693,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M66">
-        <v>5.361888</v>
+        <v>5.445667500000001</v>
       </c>
       <c r="N66">
-        <v>19.43811200000001</v>
+        <v>19.35433250000001</v>
       </c>
       <c r="O66">
-        <v>3.693241280000001</v>
+        <v>3.677323175000001</v>
       </c>
       <c r="P66">
-        <v>15.74487072000001</v>
+        <v>15.677009325</v>
       </c>
       <c r="Q66">
-        <v>34.44487072</v>
+        <v>34.377009325</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1878426142160383</v>
+        <v>0.191584954754517</v>
       </c>
       <c r="T66">
-        <v>2.395042537171372</v>
+        <v>2.458143774977409</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.625236483865386</v>
+        <v>4.554078999498225</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09617018416408096</v>
+        <v>0.09738600721038815</v>
       </c>
       <c r="C67">
-        <v>71.6735898532758</v>
+        <v>66.75645908688816</v>
       </c>
       <c r="D67">
-        <v>144.3485898532758</v>
+        <v>140.9464590868882</v>
       </c>
       <c r="E67">
-        <v>-33.72499999999998</v>
+        <v>-32.20999999999998</v>
       </c>
       <c r="F67">
-        <v>98.47500000000001</v>
+        <v>99.99000000000001</v>
       </c>
       <c r="G67">
         <v>25.8</v>
@@ -6775,45 +6775,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M67">
-        <v>5.445667500000001</v>
+        <v>5.779422000000001</v>
       </c>
       <c r="N67">
-        <v>19.35433250000001</v>
+        <v>19.02057800000001</v>
       </c>
       <c r="O67">
-        <v>3.677323175000001</v>
+        <v>3.613909820000001</v>
       </c>
       <c r="P67">
-        <v>15.677009325</v>
+        <v>15.40666818000001</v>
       </c>
       <c r="Q67">
-        <v>34.377009325</v>
+        <v>34.10666818000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.191584954754517</v>
+        <v>0.1955474329717299</v>
       </c>
       <c r="T67">
-        <v>2.458143774977409</v>
+        <v>2.524956850301448</v>
       </c>
       <c r="U67">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V67">
         <v>0.19</v>
       </c>
       <c r="W67">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.554078999498225</v>
+        <v>4.291086548101178</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09738600721038815</v>
+        <v>0.09728558025669534</v>
       </c>
       <c r="C68">
-        <v>66.75645908688816</v>
+        <v>65.51638700746925</v>
       </c>
       <c r="D68">
-        <v>140.9464590868882</v>
+        <v>141.2213870074692</v>
       </c>
       <c r="E68">
-        <v>-32.20999999999998</v>
+        <v>-30.69499999999998</v>
       </c>
       <c r="F68">
-        <v>99.99000000000001</v>
+        <v>101.505</v>
       </c>
       <c r="G68">
         <v>25.8</v>
@@ -6857,28 +6857,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M68">
-        <v>5.779422000000001</v>
+        <v>5.866989000000001</v>
       </c>
       <c r="N68">
-        <v>19.02057800000001</v>
+        <v>18.93301100000001</v>
       </c>
       <c r="O68">
-        <v>3.613909820000001</v>
+        <v>3.597272090000001</v>
       </c>
       <c r="P68">
-        <v>15.40666818000001</v>
+        <v>15.33573891000001</v>
       </c>
       <c r="Q68">
-        <v>34.10666818000001</v>
+        <v>34.03573891000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1955474329717299</v>
+        <v>0.1997500613839253</v>
       </c>
       <c r="T68">
-        <v>2.524956850301448</v>
+        <v>2.595819202917854</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.291086548101178</v>
+        <v>4.22704048021907</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09728558025669534</v>
+        <v>0.09718515330300254</v>
       </c>
       <c r="C69">
-        <v>65.51638700746925</v>
+        <v>64.27738956427402</v>
       </c>
       <c r="D69">
-        <v>141.2213870074692</v>
+        <v>141.497389564274</v>
       </c>
       <c r="E69">
-        <v>-30.69499999999998</v>
+        <v>-29.17999999999998</v>
       </c>
       <c r="F69">
-        <v>101.505</v>
+        <v>103.02</v>
       </c>
       <c r="G69">
         <v>25.8</v>
@@ -6939,28 +6939,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M69">
-        <v>5.866989000000001</v>
+        <v>5.954556000000001</v>
       </c>
       <c r="N69">
-        <v>18.93301100000001</v>
+        <v>18.84544400000001</v>
       </c>
       <c r="O69">
-        <v>3.597272090000001</v>
+        <v>3.580634360000002</v>
       </c>
       <c r="P69">
-        <v>15.33573891000001</v>
+        <v>15.26480964000001</v>
       </c>
       <c r="Q69">
-        <v>34.03573891000001</v>
+        <v>33.96480964000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1997500613839253</v>
+        <v>0.2042153540718829</v>
       </c>
       <c r="T69">
-        <v>2.595819202917854</v>
+        <v>2.671110452572785</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.22704048021907</v>
+        <v>4.164878120215849</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09718515330300254</v>
+        <v>0.0970847263493097</v>
       </c>
       <c r="C70">
-        <v>64.27738956427402</v>
+        <v>63.03947307043605</v>
       </c>
       <c r="D70">
-        <v>141.497389564274</v>
+        <v>141.774473070436</v>
       </c>
       <c r="E70">
-        <v>-29.17999999999998</v>
+        <v>-27.66499999999998</v>
       </c>
       <c r="F70">
-        <v>103.02</v>
+        <v>104.535</v>
       </c>
       <c r="G70">
         <v>25.8</v>
@@ -7021,28 +7021,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M70">
-        <v>5.954556000000001</v>
+        <v>6.042123000000001</v>
       </c>
       <c r="N70">
-        <v>18.84544400000001</v>
+        <v>18.75787700000001</v>
       </c>
       <c r="O70">
-        <v>3.580634360000002</v>
+        <v>3.563996630000001</v>
       </c>
       <c r="P70">
-        <v>15.26480964000001</v>
+        <v>15.19388037000001</v>
       </c>
       <c r="Q70">
-        <v>33.96480964000001</v>
+        <v>33.89388037000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2042153540718829</v>
+        <v>0.2089687301590636</v>
       </c>
       <c r="T70">
-        <v>2.671110452572785</v>
+        <v>2.751259202205454</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.164878120215849</v>
+        <v>4.104517567748953</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0970847263493097</v>
+        <v>0.0969842993956169</v>
       </c>
       <c r="C71">
-        <v>63.03947307043605</v>
+        <v>61.80264388863591</v>
       </c>
       <c r="D71">
-        <v>141.774473070436</v>
+        <v>142.0526438886359</v>
       </c>
       <c r="E71">
-        <v>-27.66499999999998</v>
+        <v>-26.14999999999998</v>
       </c>
       <c r="F71">
-        <v>104.535</v>
+        <v>106.05</v>
       </c>
       <c r="G71">
         <v>25.8</v>
@@ -7103,28 +7103,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M71">
-        <v>6.042123000000001</v>
+        <v>6.129690000000001</v>
       </c>
       <c r="N71">
-        <v>18.75787700000001</v>
+        <v>18.67031000000001</v>
       </c>
       <c r="O71">
-        <v>3.563996630000001</v>
+        <v>3.547358900000002</v>
       </c>
       <c r="P71">
-        <v>15.19388037000001</v>
+        <v>15.12295110000001</v>
       </c>
       <c r="Q71">
-        <v>33.89388037000001</v>
+        <v>33.8229511</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2089687301590636</v>
+        <v>0.2140389979853896</v>
       </c>
       <c r="T71">
-        <v>2.751259202205454</v>
+        <v>2.836751201813633</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.104517567748953</v>
+        <v>4.045881602495396</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0969842993956169</v>
+        <v>0.09889672244192409</v>
       </c>
       <c r="C72">
-        <v>61.80264388863591</v>
+        <v>55.17123109576276</v>
       </c>
       <c r="D72">
-        <v>142.0526438886359</v>
+        <v>136.9362310957628</v>
       </c>
       <c r="E72">
-        <v>-26.14999999999998</v>
+        <v>-24.63499999999998</v>
       </c>
       <c r="F72">
-        <v>106.05</v>
+        <v>107.565</v>
       </c>
       <c r="G72">
         <v>25.8</v>
@@ -7185,45 +7185,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M72">
-        <v>6.129690000000001</v>
+        <v>6.593734500000001</v>
       </c>
       <c r="N72">
-        <v>18.67031000000001</v>
+        <v>18.20626550000001</v>
       </c>
       <c r="O72">
-        <v>3.547358900000002</v>
+        <v>3.459190445000002</v>
       </c>
       <c r="P72">
-        <v>15.12295110000001</v>
+        <v>14.74707505500001</v>
       </c>
       <c r="Q72">
-        <v>33.8229511</v>
+        <v>33.44707505500001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2140389979853896</v>
+        <v>0.2194589394549107</v>
       </c>
       <c r="T72">
-        <v>2.836751201813633</v>
+        <v>2.928139201394791</v>
       </c>
       <c r="U72">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V72">
         <v>0.19</v>
       </c>
       <c r="W72">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.045881602495396</v>
+        <v>3.761146282125858</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09889672244192407</v>
+        <v>0.09882464548823126</v>
       </c>
       <c r="C73">
-        <v>55.17123109576283</v>
+        <v>53.84236994302297</v>
       </c>
       <c r="D73">
-        <v>136.9362310957628</v>
+        <v>137.122369943023</v>
       </c>
       <c r="E73">
-        <v>-24.63499999999999</v>
+        <v>-23.11999999999999</v>
       </c>
       <c r="F73">
-        <v>107.565</v>
+        <v>109.08</v>
       </c>
       <c r="G73">
         <v>25.8</v>
@@ -7267,28 +7267,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M73">
-        <v>6.5937345</v>
+        <v>6.686604</v>
       </c>
       <c r="N73">
-        <v>18.20626550000001</v>
+        <v>18.11339600000001</v>
       </c>
       <c r="O73">
-        <v>3.459190445000002</v>
+        <v>3.441545240000002</v>
       </c>
       <c r="P73">
-        <v>14.74707505500001</v>
+        <v>14.67185076000001</v>
       </c>
       <c r="Q73">
-        <v>33.44707505500001</v>
+        <v>33.37185076000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2194589394549106</v>
+        <v>0.2252660196008259</v>
       </c>
       <c r="T73">
-        <v>2.92813920139479</v>
+        <v>3.026054915231744</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.761146282125859</v>
+        <v>3.708908139318555</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09882464548823126</v>
+        <v>0.09875256853453843</v>
       </c>
       <c r="C74">
-        <v>53.84236994302297</v>
+        <v>52.51401552003949</v>
       </c>
       <c r="D74">
-        <v>137.122369943023</v>
+        <v>137.3090155200395</v>
       </c>
       <c r="E74">
-        <v>-23.11999999999999</v>
+        <v>-21.60499999999999</v>
       </c>
       <c r="F74">
-        <v>109.08</v>
+        <v>110.595</v>
       </c>
       <c r="G74">
         <v>25.8</v>
@@ -7349,28 +7349,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M74">
-        <v>6.686604</v>
+        <v>6.7794735</v>
       </c>
       <c r="N74">
-        <v>18.11339600000001</v>
+        <v>18.02052650000001</v>
       </c>
       <c r="O74">
-        <v>3.441545240000002</v>
+        <v>3.423900035000002</v>
       </c>
       <c r="P74">
-        <v>14.67185076000001</v>
+        <v>14.59662646500001</v>
       </c>
       <c r="Q74">
-        <v>33.37185076000001</v>
+        <v>33.296626465</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2252660196008259</v>
+        <v>0.2315032538316238</v>
       </c>
       <c r="T74">
-        <v>3.026054915231744</v>
+        <v>3.131223644908473</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.708908139318555</v>
+        <v>3.658101178505972</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09875256853453843</v>
+        <v>0.09868049158084562</v>
       </c>
       <c r="C75">
-        <v>52.51401552003949</v>
+        <v>51.18616989885443</v>
       </c>
       <c r="D75">
-        <v>137.3090155200395</v>
+        <v>137.4961698988544</v>
       </c>
       <c r="E75">
-        <v>-21.60499999999999</v>
+        <v>-20.08999999999999</v>
       </c>
       <c r="F75">
-        <v>110.595</v>
+        <v>112.11</v>
       </c>
       <c r="G75">
         <v>25.8</v>
@@ -7431,28 +7431,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M75">
-        <v>6.7794735</v>
+        <v>6.872343</v>
       </c>
       <c r="N75">
-        <v>18.02052650000001</v>
+        <v>17.92765700000001</v>
       </c>
       <c r="O75">
-        <v>3.423900035000002</v>
+        <v>3.406254830000001</v>
       </c>
       <c r="P75">
-        <v>14.59662646500001</v>
+        <v>14.52140217000001</v>
       </c>
       <c r="Q75">
-        <v>33.296626465</v>
+        <v>33.22140217</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2315032538316238</v>
+        <v>0.2382202753109447</v>
       </c>
       <c r="T75">
-        <v>3.131223644908473</v>
+        <v>3.244482276868027</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.658101178505972</v>
+        <v>3.608667378796432</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09868049158084562</v>
+        <v>0.09860841462715281</v>
       </c>
       <c r="C76">
-        <v>51.18616989885443</v>
+        <v>49.85883516282249</v>
       </c>
       <c r="D76">
-        <v>137.4961698988544</v>
+        <v>137.6838351628225</v>
       </c>
       <c r="E76">
-        <v>-20.08999999999999</v>
+        <v>-18.57499999999999</v>
       </c>
       <c r="F76">
-        <v>112.11</v>
+        <v>113.625</v>
       </c>
       <c r="G76">
         <v>25.8</v>
@@ -7513,28 +7513,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M76">
-        <v>6.872343</v>
+        <v>6.9652125</v>
       </c>
       <c r="N76">
-        <v>17.92765700000001</v>
+        <v>17.83478750000001</v>
       </c>
       <c r="O76">
-        <v>3.406254830000001</v>
+        <v>3.388609625000002</v>
       </c>
       <c r="P76">
-        <v>14.52140217000001</v>
+        <v>14.44617787500001</v>
       </c>
       <c r="Q76">
-        <v>33.22140217</v>
+        <v>33.14617787500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2382202753109447</v>
+        <v>0.2454746585086112</v>
       </c>
       <c r="T76">
-        <v>3.244482276868027</v>
+        <v>3.366801599384346</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.608667378796432</v>
+        <v>3.560551813745813</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09860841462715281</v>
+        <v>0.09853633767345998</v>
       </c>
       <c r="C77">
-        <v>49.85883516282249</v>
+        <v>48.53201340668782</v>
       </c>
       <c r="D77">
-        <v>137.6838351628225</v>
+        <v>137.8720134066878</v>
       </c>
       <c r="E77">
-        <v>-18.57499999999999</v>
+        <v>-17.05999999999999</v>
       </c>
       <c r="F77">
-        <v>113.625</v>
+        <v>115.14</v>
       </c>
       <c r="G77">
         <v>25.8</v>
@@ -7595,28 +7595,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M77">
-        <v>6.9652125</v>
+        <v>7.058082</v>
       </c>
       <c r="N77">
-        <v>17.83478750000001</v>
+        <v>17.74191800000001</v>
       </c>
       <c r="O77">
-        <v>3.388609625000002</v>
+        <v>3.370964420000002</v>
       </c>
       <c r="P77">
-        <v>14.44617787500001</v>
+        <v>14.37095358000001</v>
       </c>
       <c r="Q77">
-        <v>33.14617787500001</v>
+        <v>33.07095358000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2454746585086112</v>
+        <v>0.2533335736394166</v>
       </c>
       <c r="T77">
-        <v>3.366801599384346</v>
+        <v>3.499314198777025</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.560551813745813</v>
+        <v>3.513702447775473</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09853633767345998</v>
+        <v>0.1002106207197672</v>
       </c>
       <c r="C78">
-        <v>48.53201340668782</v>
+        <v>42.77451862251803</v>
       </c>
       <c r="D78">
-        <v>137.8720134066878</v>
+        <v>133.629518622518</v>
       </c>
       <c r="E78">
-        <v>-17.05999999999999</v>
+        <v>-15.54499999999999</v>
       </c>
       <c r="F78">
-        <v>115.14</v>
+        <v>116.655</v>
       </c>
       <c r="G78">
         <v>25.8</v>
@@ -7677,45 +7677,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M78">
-        <v>7.058082</v>
+        <v>7.477585500000001</v>
       </c>
       <c r="N78">
-        <v>17.74191800000001</v>
+        <v>17.32241450000001</v>
       </c>
       <c r="O78">
-        <v>3.370964420000002</v>
+        <v>3.291258755000002</v>
       </c>
       <c r="P78">
-        <v>14.37095358000001</v>
+        <v>14.03115574500001</v>
       </c>
       <c r="Q78">
-        <v>33.07095358000001</v>
+        <v>32.73115574500001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2533335736394166</v>
+        <v>0.2618758726946399</v>
       </c>
       <c r="T78">
-        <v>3.499314198777025</v>
+        <v>3.643349632899501</v>
       </c>
       <c r="U78">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V78">
         <v>0.19</v>
       </c>
       <c r="W78">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.513702447775473</v>
+        <v>3.316578593451055</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1002106207197672</v>
+        <v>0.1001612237660744</v>
       </c>
       <c r="C79">
-        <v>42.77451862251803</v>
+        <v>41.38094508583298</v>
       </c>
       <c r="D79">
-        <v>133.629518622518</v>
+        <v>133.750945085833</v>
       </c>
       <c r="E79">
-        <v>-15.54499999999999</v>
+        <v>-14.02999999999999</v>
       </c>
       <c r="F79">
-        <v>116.655</v>
+        <v>118.17</v>
       </c>
       <c r="G79">
         <v>25.8</v>
@@ -7759,28 +7759,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M79">
-        <v>7.477585500000001</v>
+        <v>7.574697</v>
       </c>
       <c r="N79">
-        <v>17.32241450000001</v>
+        <v>17.22530300000001</v>
       </c>
       <c r="O79">
-        <v>3.291258755000002</v>
+        <v>3.272807570000001</v>
       </c>
       <c r="P79">
-        <v>14.03115574500001</v>
+        <v>13.95249543000001</v>
       </c>
       <c r="Q79">
-        <v>32.73115574500001</v>
+        <v>32.65249543</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2618758726946399</v>
+        <v>0.2711947443912471</v>
       </c>
       <c r="T79">
-        <v>3.643349632899501</v>
+        <v>3.800479197396748</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.316578593451055</v>
+        <v>3.274058355073478</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1001612237660744</v>
+        <v>0.1001118268123815</v>
       </c>
       <c r="C80">
-        <v>41.38094508583298</v>
+        <v>39.98759242543727</v>
       </c>
       <c r="D80">
-        <v>133.750945085833</v>
+        <v>133.8725924254373</v>
       </c>
       <c r="E80">
-        <v>-14.02999999999999</v>
+        <v>-12.51499999999999</v>
       </c>
       <c r="F80">
-        <v>118.17</v>
+        <v>119.685</v>
       </c>
       <c r="G80">
         <v>25.8</v>
@@ -7841,28 +7841,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M80">
-        <v>7.574697</v>
+        <v>7.671808500000001</v>
       </c>
       <c r="N80">
-        <v>17.22530300000001</v>
+        <v>17.12819150000001</v>
       </c>
       <c r="O80">
-        <v>3.272807570000001</v>
+        <v>3.254356385000001</v>
       </c>
       <c r="P80">
-        <v>13.95249543000001</v>
+        <v>13.87383511500001</v>
       </c>
       <c r="Q80">
-        <v>32.65249543</v>
+        <v>32.57383511500001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2711947443912471</v>
+        <v>0.2814011276780073</v>
       </c>
       <c r="T80">
-        <v>3.800479197396748</v>
+        <v>3.972573482322305</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.274058355073478</v>
+        <v>3.232614578426978</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1001118268123815</v>
+        <v>0.1000624298586887</v>
       </c>
       <c r="C81">
-        <v>39.98759242543727</v>
+        <v>38.59446124454466</v>
       </c>
       <c r="D81">
-        <v>133.8725924254373</v>
+        <v>133.9944612445447</v>
       </c>
       <c r="E81">
-        <v>-12.51499999999999</v>
+        <v>-10.99999999999999</v>
       </c>
       <c r="F81">
-        <v>119.685</v>
+        <v>121.2</v>
       </c>
       <c r="G81">
         <v>25.8</v>
@@ -7923,28 +7923,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M81">
-        <v>7.671808500000001</v>
+        <v>7.76892</v>
       </c>
       <c r="N81">
-        <v>17.12819150000001</v>
+        <v>17.03108000000001</v>
       </c>
       <c r="O81">
-        <v>3.254356385000001</v>
+        <v>3.235905200000001</v>
       </c>
       <c r="P81">
-        <v>13.87383511500001</v>
+        <v>13.79517480000001</v>
       </c>
       <c r="Q81">
-        <v>32.57383511500001</v>
+        <v>32.4951748</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2814011276780073</v>
+        <v>0.2926281492934437</v>
       </c>
       <c r="T81">
-        <v>3.972573482322305</v>
+        <v>4.161877195740417</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.232614578426978</v>
+        <v>3.192206896196641</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1000624298586887</v>
+        <v>0.1000130329049959</v>
       </c>
       <c r="C82">
-        <v>38.59446124454466</v>
+        <v>37.20155214856752</v>
       </c>
       <c r="D82">
-        <v>133.9944612445447</v>
+        <v>134.1165521485675</v>
       </c>
       <c r="E82">
-        <v>-10.99999999999999</v>
+        <v>-9.484999999999985</v>
       </c>
       <c r="F82">
-        <v>121.2</v>
+        <v>122.715</v>
       </c>
       <c r="G82">
         <v>25.8</v>
@@ -8005,28 +8005,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M82">
-        <v>7.76892</v>
+        <v>7.866031500000001</v>
       </c>
       <c r="N82">
-        <v>17.03108000000001</v>
+        <v>16.93396850000001</v>
       </c>
       <c r="O82">
-        <v>3.235905200000001</v>
+        <v>3.217454015000001</v>
       </c>
       <c r="P82">
-        <v>13.79517480000001</v>
+        <v>13.716514485</v>
       </c>
       <c r="Q82">
-        <v>32.4951748</v>
+        <v>32.41651448500001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2926281492934437</v>
+        <v>0.3050369626578732</v>
       </c>
       <c r="T82">
-        <v>4.161877195740417</v>
+        <v>4.37110761583412</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.192206896196641</v>
+        <v>3.1527969345152</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1000130329049959</v>
+        <v>0.09996363595130309</v>
       </c>
       <c r="C83">
-        <v>37.20155214856752</v>
+        <v>35.80886574512665</v>
       </c>
       <c r="D83">
-        <v>134.1165521485675</v>
+        <v>134.2388657451266</v>
       </c>
       <c r="E83">
-        <v>-9.484999999999985</v>
+        <v>-7.969999999999985</v>
       </c>
       <c r="F83">
-        <v>122.715</v>
+        <v>124.23</v>
       </c>
       <c r="G83">
         <v>25.8</v>
@@ -8087,28 +8087,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M83">
-        <v>7.866031500000001</v>
+        <v>7.963143000000001</v>
       </c>
       <c r="N83">
-        <v>16.93396850000001</v>
+        <v>16.83685700000001</v>
       </c>
       <c r="O83">
-        <v>3.217454015000001</v>
+        <v>3.199002830000002</v>
       </c>
       <c r="P83">
-        <v>13.716514485</v>
+        <v>13.63785417000001</v>
       </c>
       <c r="Q83">
-        <v>32.41651448500001</v>
+        <v>32.33785417000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3050369626578732</v>
+        <v>0.318824533062795</v>
       </c>
       <c r="T83">
-        <v>4.37110761583412</v>
+        <v>4.603585860382678</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.1527969345152</v>
+        <v>3.114348191411357</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09996363595130309</v>
+        <v>0.09991423899761026</v>
       </c>
       <c r="C84">
-        <v>35.80886574512665</v>
+        <v>34.41640264406158</v>
       </c>
       <c r="D84">
-        <v>134.2388657451266</v>
+        <v>134.3614026440616</v>
       </c>
       <c r="E84">
-        <v>-7.969999999999985</v>
+        <v>-6.454999999999984</v>
       </c>
       <c r="F84">
-        <v>124.23</v>
+        <v>125.745</v>
       </c>
       <c r="G84">
         <v>25.8</v>
@@ -8169,28 +8169,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M84">
-        <v>7.963143000000001</v>
+        <v>8.060254500000001</v>
       </c>
       <c r="N84">
-        <v>16.83685700000001</v>
+        <v>16.73974550000001</v>
       </c>
       <c r="O84">
-        <v>3.199002830000002</v>
+        <v>3.180551645000001</v>
       </c>
       <c r="P84">
-        <v>13.63785417000001</v>
+        <v>13.559193855</v>
       </c>
       <c r="Q84">
-        <v>32.33785417000001</v>
+        <v>32.25919385500001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.318824533062795</v>
+        <v>0.3342341705741781</v>
       </c>
       <c r="T84">
-        <v>4.603585860382678</v>
+        <v>4.863414486642832</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.114348191411357</v>
+        <v>3.076825924044955</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09991423899761026</v>
+        <v>0.09986484204391745</v>
       </c>
       <c r="C85">
-        <v>34.41640264406158</v>
+        <v>33.02416345744039</v>
       </c>
       <c r="D85">
-        <v>134.3614026440616</v>
+        <v>134.4841634574404</v>
       </c>
       <c r="E85">
-        <v>-6.454999999999984</v>
+        <v>-4.939999999999984</v>
       </c>
       <c r="F85">
-        <v>125.745</v>
+        <v>127.26</v>
       </c>
       <c r="G85">
         <v>25.8</v>
@@ -8251,28 +8251,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M85">
-        <v>8.060254500000001</v>
+        <v>8.157366000000001</v>
       </c>
       <c r="N85">
-        <v>16.73974550000001</v>
+        <v>16.64263400000001</v>
       </c>
       <c r="O85">
-        <v>3.180551645000001</v>
+        <v>3.162100460000002</v>
       </c>
       <c r="P85">
-        <v>13.559193855</v>
+        <v>13.48053354000001</v>
       </c>
       <c r="Q85">
-        <v>32.25919385500001</v>
+        <v>32.18053354000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3342341705741781</v>
+        <v>0.3515700127744842</v>
       </c>
       <c r="T85">
-        <v>4.863414486642832</v>
+        <v>5.155721691185506</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.076825924044955</v>
+        <v>3.0401970439968</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09986484204391746</v>
+        <v>0.09981544509022465</v>
       </c>
       <c r="C86">
-        <v>33.02416345744038</v>
+        <v>31.63214879957036</v>
       </c>
       <c r="D86">
-        <v>134.4841634574404</v>
+        <v>134.6071487995704</v>
       </c>
       <c r="E86">
-        <v>-4.939999999999998</v>
+        <v>-3.424999999999983</v>
       </c>
       <c r="F86">
-        <v>127.26</v>
+        <v>128.775</v>
       </c>
       <c r="G86">
         <v>25.8</v>
@@ -8333,28 +8333,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M86">
-        <v>8.157366</v>
+        <v>8.2544775</v>
       </c>
       <c r="N86">
-        <v>16.64263400000001</v>
+        <v>16.54552250000001</v>
       </c>
       <c r="O86">
-        <v>3.162100460000002</v>
+        <v>3.143649275000001</v>
       </c>
       <c r="P86">
-        <v>13.48053354000001</v>
+        <v>13.40187322500001</v>
       </c>
       <c r="Q86">
-        <v>32.18053354000001</v>
+        <v>32.10187322500001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.351570012774484</v>
+        <v>0.3712173006014975</v>
       </c>
       <c r="T86">
-        <v>5.155721691185502</v>
+        <v>5.487003189667199</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.040197043996801</v>
+        <v>3.00443001994978</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09981544509022465</v>
+        <v>0.1051995281365318</v>
       </c>
       <c r="C87">
-        <v>31.63214879957036</v>
+        <v>17.91610797484049</v>
       </c>
       <c r="D87">
-        <v>134.6071487995704</v>
+        <v>122.4061079748405</v>
       </c>
       <c r="E87">
-        <v>-3.424999999999983</v>
+        <v>-1.909999999999997</v>
       </c>
       <c r="F87">
-        <v>128.775</v>
+        <v>130.29</v>
       </c>
       <c r="G87">
         <v>25.8</v>
@@ -8415,45 +8415,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M87">
-        <v>8.2544775</v>
+        <v>9.367851</v>
       </c>
       <c r="N87">
-        <v>16.54552250000001</v>
+        <v>15.43214900000001</v>
       </c>
       <c r="O87">
-        <v>3.143649275000001</v>
+        <v>2.932108310000002</v>
       </c>
       <c r="P87">
-        <v>13.40187322500001</v>
+        <v>12.50004069000001</v>
       </c>
       <c r="Q87">
-        <v>32.10187322500001</v>
+        <v>31.20004069000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3712173006014975</v>
+        <v>0.3936713438323701</v>
       </c>
       <c r="T87">
-        <v>5.487003189667199</v>
+        <v>5.865610616503424</v>
       </c>
       <c r="U87">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V87">
         <v>0.19</v>
       </c>
       <c r="W87">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.00443001994978</v>
+        <v>2.647352098149299</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1051995281365318</v>
+        <v>0.105213311182839</v>
       </c>
       <c r="C88">
-        <v>17.91610797484049</v>
+        <v>16.37271149228616</v>
       </c>
       <c r="D88">
-        <v>122.4061079748405</v>
+        <v>122.3777114922862</v>
       </c>
       <c r="E88">
-        <v>-1.909999999999997</v>
+        <v>-0.3949999999999818</v>
       </c>
       <c r="F88">
-        <v>130.29</v>
+        <v>131.805</v>
       </c>
       <c r="G88">
         <v>25.8</v>
@@ -8497,28 +8497,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M88">
-        <v>9.367851</v>
+        <v>9.476779500000001</v>
       </c>
       <c r="N88">
-        <v>15.43214900000001</v>
+        <v>15.32322050000001</v>
       </c>
       <c r="O88">
-        <v>2.932108310000002</v>
+        <v>2.911411895000001</v>
       </c>
       <c r="P88">
-        <v>12.50004069000001</v>
+        <v>12.411808605</v>
       </c>
       <c r="Q88">
-        <v>31.20004069000001</v>
+        <v>31.111808605</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3936713438323701</v>
+        <v>0.4195798552526077</v>
       </c>
       <c r="T88">
-        <v>5.865610616503424</v>
+        <v>6.302465339775988</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.647352098149299</v>
+        <v>2.616922763687812</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.105213311182839</v>
+        <v>0.1052270942291462</v>
       </c>
       <c r="C89">
-        <v>16.37271149228616</v>
+        <v>14.8293281818392</v>
       </c>
       <c r="D89">
-        <v>122.3777114922862</v>
+        <v>122.3493281818392</v>
       </c>
       <c r="E89">
-        <v>-0.3949999999999818</v>
+        <v>1.120000000000005</v>
       </c>
       <c r="F89">
-        <v>131.805</v>
+        <v>133.32</v>
       </c>
       <c r="G89">
         <v>25.8</v>
@@ -8579,28 +8579,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M89">
-        <v>9.476779500000001</v>
+        <v>9.585708</v>
       </c>
       <c r="N89">
-        <v>15.32322050000001</v>
+        <v>15.21429200000001</v>
       </c>
       <c r="O89">
-        <v>2.911411895000001</v>
+        <v>2.890715480000002</v>
       </c>
       <c r="P89">
-        <v>12.411808605</v>
+        <v>12.32357652000001</v>
       </c>
       <c r="Q89">
-        <v>31.111808605</v>
+        <v>31.02357652000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4195798552526077</v>
+        <v>0.4498064519095516</v>
       </c>
       <c r="T89">
-        <v>6.302465339775988</v>
+        <v>6.812129183593984</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.616922763687812</v>
+        <v>2.587185005009542</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1052270942291462</v>
+        <v>0.1052408772754534</v>
       </c>
       <c r="C90">
-        <v>14.8293281818392</v>
+        <v>13.28595803433672</v>
       </c>
       <c r="D90">
-        <v>122.3493281818392</v>
+        <v>122.3209580343367</v>
       </c>
       <c r="E90">
-        <v>1.120000000000005</v>
+        <v>2.635000000000019</v>
       </c>
       <c r="F90">
-        <v>133.32</v>
+        <v>134.835</v>
       </c>
       <c r="G90">
         <v>25.8</v>
@@ -8661,28 +8661,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M90">
-        <v>9.585708</v>
+        <v>9.694636500000001</v>
       </c>
       <c r="N90">
-        <v>15.21429200000001</v>
+        <v>15.10536350000001</v>
       </c>
       <c r="O90">
-        <v>2.890715480000002</v>
+        <v>2.870019065000001</v>
       </c>
       <c r="P90">
-        <v>12.32357652000001</v>
+        <v>12.23534443500001</v>
       </c>
       <c r="Q90">
-        <v>31.02357652000001</v>
+        <v>30.935344435</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4498064519095516</v>
+        <v>0.4855287934132125</v>
       </c>
       <c r="T90">
-        <v>6.812129183593984</v>
+        <v>7.414459180833431</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.587185005009542</v>
+        <v>2.558115510571232</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1052408772754534</v>
+        <v>0.1052546603217606</v>
       </c>
       <c r="C91">
-        <v>13.28595803433672</v>
+        <v>11.74260104062415</v>
       </c>
       <c r="D91">
-        <v>122.3209580343367</v>
+        <v>122.2926010406241</v>
       </c>
       <c r="E91">
-        <v>2.635000000000019</v>
+        <v>4.150000000000006</v>
       </c>
       <c r="F91">
-        <v>134.835</v>
+        <v>136.35</v>
       </c>
       <c r="G91">
         <v>25.8</v>
@@ -8743,28 +8743,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M91">
-        <v>9.694636500000001</v>
+        <v>9.803565000000001</v>
       </c>
       <c r="N91">
-        <v>15.10536350000001</v>
+        <v>14.99643500000001</v>
       </c>
       <c r="O91">
-        <v>2.870019065000001</v>
+        <v>2.849322650000001</v>
       </c>
       <c r="P91">
-        <v>12.23534443500001</v>
+        <v>12.14711235000001</v>
       </c>
       <c r="Q91">
-        <v>30.935344435</v>
+        <v>30.84711235</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4855287934132125</v>
+        <v>0.5283956032176057</v>
       </c>
       <c r="T91">
-        <v>7.414459180833431</v>
+        <v>8.137255177520769</v>
       </c>
       <c r="U91">
         <v>0.07190000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.558115510571232</v>
+        <v>2.529692004898219</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1052546603217606</v>
+        <v>0.1052684433680677</v>
       </c>
       <c r="C92">
-        <v>11.74260104062415</v>
+        <v>10.19925719155557</v>
       </c>
       <c r="D92">
-        <v>122.2926010406241</v>
+        <v>122.2642571915556</v>
       </c>
       <c r="E92">
-        <v>4.150000000000006</v>
+        <v>5.66500000000002</v>
       </c>
       <c r="F92">
-        <v>136.35</v>
+        <v>137.865</v>
       </c>
       <c r="G92">
         <v>25.8</v>
@@ -8825,28 +8825,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M92">
-        <v>9.803565000000001</v>
+        <v>9.912493500000002</v>
       </c>
       <c r="N92">
-        <v>14.99643500000001</v>
+        <v>14.88750650000001</v>
       </c>
       <c r="O92">
-        <v>2.849322650000001</v>
+        <v>2.828626235000001</v>
       </c>
       <c r="P92">
-        <v>12.14711235000001</v>
+        <v>12.058880265</v>
       </c>
       <c r="Q92">
-        <v>30.84711235</v>
+        <v>30.758880265</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5283956032176057</v>
+        <v>0.5807883707563082</v>
       </c>
       <c r="T92">
-        <v>8.137255177520769</v>
+        <v>9.02067250680529</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.529692004898219</v>
+        <v>2.501893191657579</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1052684433680677</v>
+        <v>0.1081885064143749</v>
       </c>
       <c r="C93">
-        <v>10.19925719155557</v>
+        <v>2.961739378130289</v>
       </c>
       <c r="D93">
-        <v>122.2642571915556</v>
+        <v>116.5417393781303</v>
       </c>
       <c r="E93">
-        <v>5.66500000000002</v>
+        <v>7.180000000000007</v>
       </c>
       <c r="F93">
-        <v>137.865</v>
+        <v>139.38</v>
       </c>
       <c r="G93">
         <v>25.8</v>
@@ -8907,45 +8907,45 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M93">
-        <v>9.912493500000002</v>
+        <v>10.565004</v>
       </c>
       <c r="N93">
-        <v>14.88750650000001</v>
+        <v>14.23499600000001</v>
       </c>
       <c r="O93">
-        <v>2.828626235000001</v>
+        <v>2.704649240000002</v>
       </c>
       <c r="P93">
-        <v>12.058880265</v>
+        <v>11.53034676000001</v>
       </c>
       <c r="Q93">
-        <v>30.758880265</v>
+        <v>30.23034676</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5807883707563082</v>
+        <v>0.6462793301796868</v>
       </c>
       <c r="T93">
-        <v>9.02067250680529</v>
+        <v>10.12494416841095</v>
       </c>
       <c r="U93">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V93">
         <v>0.19</v>
       </c>
       <c r="W93">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.501893191657579</v>
+        <v>2.347372514009461</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1081885064143749</v>
+        <v>0.1082338794606821</v>
       </c>
       <c r="C94">
-        <v>2.961739378130289</v>
+        <v>1.362044116788212</v>
       </c>
       <c r="D94">
-        <v>116.5417393781303</v>
+        <v>116.4570441167882</v>
       </c>
       <c r="E94">
-        <v>7.180000000000007</v>
+        <v>8.695000000000022</v>
       </c>
       <c r="F94">
-        <v>139.38</v>
+        <v>140.895</v>
       </c>
       <c r="G94">
         <v>25.8</v>
@@ -8989,28 +8989,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M94">
-        <v>10.565004</v>
+        <v>10.679841</v>
       </c>
       <c r="N94">
-        <v>14.23499600000001</v>
+        <v>14.12015900000001</v>
       </c>
       <c r="O94">
-        <v>2.704649240000002</v>
+        <v>2.682830210000001</v>
       </c>
       <c r="P94">
-        <v>11.53034676000001</v>
+        <v>11.43732879000001</v>
       </c>
       <c r="Q94">
-        <v>30.23034676</v>
+        <v>30.13732879000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6462793301796868</v>
+        <v>0.7304819922954588</v>
       </c>
       <c r="T94">
-        <v>10.12494416841095</v>
+        <v>11.54472201904679</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.347372514009461</v>
+        <v>2.322131949342692</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1082338794606821</v>
+        <v>0.1082792525069893</v>
       </c>
       <c r="C95">
-        <v>1.362044116788212</v>
+        <v>-0.2375281314940594</v>
       </c>
       <c r="D95">
-        <v>116.4570441167882</v>
+        <v>116.3724718685059</v>
       </c>
       <c r="E95">
-        <v>8.695000000000022</v>
+        <v>10.21000000000001</v>
       </c>
       <c r="F95">
-        <v>140.895</v>
+        <v>142.41</v>
       </c>
       <c r="G95">
         <v>25.8</v>
@@ -9071,28 +9071,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M95">
-        <v>10.679841</v>
+        <v>10.794678</v>
       </c>
       <c r="N95">
-        <v>14.12015900000001</v>
+        <v>14.00532200000001</v>
       </c>
       <c r="O95">
-        <v>2.682830210000001</v>
+        <v>2.661011180000001</v>
       </c>
       <c r="P95">
-        <v>11.43732879000001</v>
+        <v>11.34431082000001</v>
       </c>
       <c r="Q95">
-        <v>30.13732879000001</v>
+        <v>30.04431082000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7304819922954588</v>
+        <v>0.842752208449822</v>
       </c>
       <c r="T95">
-        <v>11.54472201904679</v>
+        <v>13.43775915322791</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.322131949342692</v>
+        <v>2.297428417966706</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1082792525069893</v>
+        <v>0.1083246255532965</v>
       </c>
       <c r="C96">
-        <v>-0.2375281314940594</v>
+        <v>-1.836977634521816</v>
       </c>
       <c r="D96">
-        <v>116.3724718685059</v>
+        <v>116.2880223654782</v>
       </c>
       <c r="E96">
-        <v>10.21000000000001</v>
+        <v>11.72500000000002</v>
       </c>
       <c r="F96">
-        <v>142.41</v>
+        <v>143.925</v>
       </c>
       <c r="G96">
         <v>25.8</v>
@@ -9153,28 +9153,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M96">
-        <v>10.794678</v>
+        <v>10.909515</v>
       </c>
       <c r="N96">
-        <v>14.00532200000001</v>
+        <v>13.89048500000001</v>
       </c>
       <c r="O96">
-        <v>2.661011180000001</v>
+        <v>2.639192150000001</v>
       </c>
       <c r="P96">
-        <v>11.34431082000001</v>
+        <v>11.25129285</v>
       </c>
       <c r="Q96">
-        <v>30.04431082000001</v>
+        <v>29.95129285</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.842752208449822</v>
+        <v>0.9999305110659304</v>
       </c>
       <c r="T96">
-        <v>13.43775915322791</v>
+        <v>16.08801114108149</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.297428417966706</v>
+        <v>2.273244960935477</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1083246255532965</v>
+        <v>0.1083699985996037</v>
       </c>
       <c r="C97">
-        <v>-1.836977634521816</v>
+        <v>-3.436304659323639</v>
       </c>
       <c r="D97">
-        <v>116.2880223654782</v>
+        <v>116.2036953406763</v>
       </c>
       <c r="E97">
-        <v>11.72500000000002</v>
+        <v>13.24000000000001</v>
       </c>
       <c r="F97">
-        <v>143.925</v>
+        <v>145.44</v>
       </c>
       <c r="G97">
         <v>25.8</v>
@@ -9235,28 +9235,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M97">
-        <v>10.909515</v>
+        <v>11.024352</v>
       </c>
       <c r="N97">
-        <v>13.89048500000001</v>
+        <v>13.77564800000001</v>
       </c>
       <c r="O97">
-        <v>2.639192150000001</v>
+        <v>2.617373120000002</v>
       </c>
       <c r="P97">
-        <v>11.25129285</v>
+        <v>11.15827488000001</v>
       </c>
       <c r="Q97">
-        <v>29.95129285</v>
+        <v>29.85827488</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9999305110659304</v>
+        <v>1.235697964990094</v>
       </c>
       <c r="T97">
-        <v>16.08801114108149</v>
+        <v>20.06338912286186</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.273244960935477</v>
+        <v>2.249565325925733</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1083699985996037</v>
+        <v>0.1084153716459108</v>
       </c>
       <c r="C98">
-        <v>-3.436304659323639</v>
+        <v>-5.035509472154132</v>
       </c>
       <c r="D98">
-        <v>116.2036953406763</v>
+        <v>116.1194905278458</v>
       </c>
       <c r="E98">
-        <v>13.24000000000001</v>
+        <v>14.755</v>
       </c>
       <c r="F98">
-        <v>145.44</v>
+        <v>146.955</v>
       </c>
       <c r="G98">
         <v>25.8</v>
@@ -9317,28 +9317,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M98">
-        <v>11.024352</v>
+        <v>11.139189</v>
       </c>
       <c r="N98">
-        <v>13.77564800000001</v>
+        <v>13.66081100000001</v>
       </c>
       <c r="O98">
-        <v>2.617373120000002</v>
+        <v>2.595554090000002</v>
       </c>
       <c r="P98">
-        <v>11.15827488000001</v>
+        <v>11.06525691000001</v>
       </c>
       <c r="Q98">
-        <v>29.85827488</v>
+        <v>29.76525691000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.23569796499009</v>
+        <v>1.62864372153036</v>
       </c>
       <c r="T98">
-        <v>20.0633891228618</v>
+        <v>26.68901909249571</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.249565325925733</v>
+        <v>2.226373930813097</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1084153716459108</v>
+        <v>0.108460744692218</v>
       </c>
       <c r="C99">
-        <v>-5.035509472154132</v>
+        <v>-6.634592338496816</v>
       </c>
       <c r="D99">
-        <v>116.1194905278458</v>
+        <v>116.0354076615032</v>
       </c>
       <c r="E99">
-        <v>14.755</v>
+        <v>16.27000000000001</v>
       </c>
       <c r="F99">
-        <v>146.955</v>
+        <v>148.47</v>
       </c>
       <c r="G99">
         <v>25.8</v>
@@ -9399,28 +9399,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M99">
-        <v>11.139189</v>
+        <v>11.254026</v>
       </c>
       <c r="N99">
-        <v>13.66081100000001</v>
+        <v>13.54597400000001</v>
       </c>
       <c r="O99">
-        <v>2.595554090000002</v>
+        <v>2.573735060000001</v>
       </c>
       <c r="P99">
-        <v>11.06525691000001</v>
+        <v>10.97223894000001</v>
       </c>
       <c r="Q99">
-        <v>29.76525691000001</v>
+        <v>29.67223894000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.62864372153036</v>
+        <v>2.414535234610899</v>
       </c>
       <c r="T99">
-        <v>26.68901909249571</v>
+        <v>39.94027903176354</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.226373930813097</v>
+        <v>2.203655829478269</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.108460744692218</v>
+        <v>0.1085061177385252</v>
       </c>
       <c r="C100">
-        <v>-6.634592338496816</v>
+        <v>-8.233553523066576</v>
       </c>
       <c r="D100">
-        <v>116.0354076615032</v>
+        <v>115.9514464769334</v>
       </c>
       <c r="E100">
-        <v>16.27000000000001</v>
+        <v>17.785</v>
       </c>
       <c r="F100">
-        <v>148.47</v>
+        <v>149.985</v>
       </c>
       <c r="G100">
         <v>25.8</v>
@@ -9481,28 +9481,28 @@
         <v>24.80000000000001</v>
       </c>
       <c r="M100">
-        <v>11.254026</v>
+        <v>11.368863</v>
       </c>
       <c r="N100">
-        <v>13.54597400000001</v>
+        <v>13.43113700000001</v>
       </c>
       <c r="O100">
-        <v>2.573735060000001</v>
+        <v>2.551916030000001</v>
       </c>
       <c r="P100">
-        <v>10.97223894000001</v>
+        <v>10.87922097000001</v>
       </c>
       <c r="Q100">
-        <v>29.67223894000001</v>
+        <v>29.57922097000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.414535234610899</v>
+        <v>4.772209773852516</v>
       </c>
       <c r="T100">
-        <v>39.94027903176354</v>
+        <v>79.69405884956701</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.203655829478269</v>
+        <v>2.18139667968556</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1085061177385252</v>
-      </c>
-      <c r="C101">
-        <v>-8.233553523066576</v>
-      </c>
-      <c r="D101">
-        <v>115.9514464769334</v>
-      </c>
-      <c r="E101">
-        <v>17.785</v>
-      </c>
-      <c r="F101">
-        <v>149.985</v>
-      </c>
-      <c r="G101">
-        <v>25.8</v>
-      </c>
-      <c r="H101">
-        <v>19.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>43.50000000000001</v>
-      </c>
-      <c r="K101">
-        <v>18.7</v>
-      </c>
-      <c r="L101">
-        <v>24.80000000000001</v>
-      </c>
-      <c r="M101">
-        <v>11.368863</v>
-      </c>
-      <c r="N101">
-        <v>13.43113700000001</v>
-      </c>
-      <c r="O101">
-        <v>2.551916030000001</v>
-      </c>
-      <c r="P101">
-        <v>10.87922097000001</v>
-      </c>
-      <c r="Q101">
-        <v>29.57922097000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.772209773852516</v>
-      </c>
-      <c r="T101">
-        <v>79.69405884956701</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.19</v>
-      </c>
-      <c r="W101">
-        <v>0.06139800000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.18139667968556</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
